--- a/research/traditional_assets/database/data/thailand/thailand_transportation_railroads.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_transportation_railroads.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07770391977759009</v>
+        <v>0.07758451193803489</v>
       </c>
       <c r="C2">
-        <v>8337.705258021319</v>
+        <v>8292.541307752954</v>
       </c>
       <c r="D2">
-        <v>8155.905258021318</v>
+        <v>8186.545307752955</v>
       </c>
       <c r="E2">
-        <v>-5240.2</v>
+        <v>-5164.396</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>75.804</v>
       </c>
       <c r="G2">
         <v>181.8</v>
@@ -1439,28 +1439,28 @@
         <v>74.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.8129412</v>
       </c>
       <c r="N2">
-        <v>74.5</v>
+        <v>70.6870588</v>
       </c>
       <c r="O2">
-        <v>14.9</v>
+        <v>14.13741176</v>
       </c>
       <c r="P2">
-        <v>59.6</v>
+        <v>56.54964704</v>
       </c>
       <c r="Q2">
-        <v>84.09999999999999</v>
+        <v>81.04964704</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07770391977759009</v>
+        <v>0.07796172923033828</v>
       </c>
       <c r="T2">
-        <v>0.4935434922969562</v>
+        <v>0.4975317225377397</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>19.53872249590421</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07758451193803489</v>
+        <v>0.07751630409847972</v>
       </c>
       <c r="C3">
-        <v>8292.541307752954</v>
+        <v>8234.342970983089</v>
       </c>
       <c r="D3">
-        <v>8186.545307752955</v>
+        <v>8204.15097098309</v>
       </c>
       <c r="E3">
-        <v>-5164.396</v>
+        <v>-5088.592</v>
       </c>
       <c r="F3">
-        <v>75.804</v>
+        <v>151.608</v>
       </c>
       <c r="G3">
         <v>181.8</v>
@@ -1521,45 +1521,45 @@
         <v>74.5</v>
       </c>
       <c r="M3">
-        <v>3.8129412</v>
+        <v>8.111027999999999</v>
       </c>
       <c r="N3">
-        <v>70.6870588</v>
+        <v>66.388972</v>
       </c>
       <c r="O3">
-        <v>14.13741176</v>
+        <v>13.2777944</v>
       </c>
       <c r="P3">
-        <v>56.54964704</v>
+        <v>53.1111776</v>
       </c>
       <c r="Q3">
-        <v>81.04964704</v>
+        <v>77.61117759999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07796172923033828</v>
+        <v>0.07822480010048952</v>
       </c>
       <c r="T3">
-        <v>0.4975317225377397</v>
+        <v>0.5016013452324167</v>
       </c>
       <c r="U3">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V3">
         <v>0.2</v>
       </c>
       <c r="W3">
-        <v>0.04024</v>
+        <v>0.0428</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y3">
-        <v>19.53872249590421</v>
+        <v>9.185025621906373</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07751630409847972</v>
+        <v>0.07746569625892455</v>
       </c>
       <c r="C4">
-        <v>8234.342970983089</v>
+        <v>8171.650773503738</v>
       </c>
       <c r="D4">
-        <v>8204.15097098309</v>
+        <v>8217.262773503739</v>
       </c>
       <c r="E4">
-        <v>-5088.592</v>
+        <v>-5012.788</v>
       </c>
       <c r="F4">
-        <v>151.608</v>
+        <v>227.412</v>
       </c>
       <c r="G4">
         <v>181.8</v>
@@ -1603,45 +1603,45 @@
         <v>74.5</v>
       </c>
       <c r="M4">
-        <v>8.111027999999999</v>
+        <v>12.5758836</v>
       </c>
       <c r="N4">
-        <v>66.388972</v>
+        <v>61.9241164</v>
       </c>
       <c r="O4">
-        <v>13.2777944</v>
+        <v>12.38482328</v>
       </c>
       <c r="P4">
-        <v>53.1111776</v>
+        <v>49.53929312</v>
       </c>
       <c r="Q4">
-        <v>77.61117759999999</v>
+        <v>74.03929312</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07822480010048952</v>
+        <v>0.07849329511229335</v>
       </c>
       <c r="T4">
-        <v>0.5016013452324167</v>
+        <v>0.5057548776733757</v>
       </c>
       <c r="U4">
-        <v>0.0535</v>
+        <v>0.0553</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.0428</v>
+        <v>0.04424</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y4">
-        <v>9.185025621906373</v>
+        <v>5.92403701955384</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07746569625892455</v>
+        <v>0.07746628841936937</v>
       </c>
       <c r="C5">
-        <v>8171.650773503738</v>
+        <v>8095.693110468945</v>
       </c>
       <c r="D5">
-        <v>8217.262773503739</v>
+        <v>8217.109110468946</v>
       </c>
       <c r="E5">
-        <v>-5012.788</v>
+        <v>-4936.983999999999</v>
       </c>
       <c r="F5">
-        <v>227.412</v>
+        <v>303.216</v>
       </c>
       <c r="G5">
         <v>181.8</v>
@@ -1685,45 +1685,45 @@
         <v>74.5</v>
       </c>
       <c r="M5">
-        <v>12.5758836</v>
+        <v>17.5258848</v>
       </c>
       <c r="N5">
-        <v>61.9241164</v>
+        <v>56.9741152</v>
       </c>
       <c r="O5">
-        <v>12.38482328</v>
+        <v>11.39482304</v>
       </c>
       <c r="P5">
-        <v>49.53929312</v>
+        <v>45.57929216</v>
       </c>
       <c r="Q5">
-        <v>74.03929312</v>
+        <v>70.07929215999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07849329511229335</v>
+        <v>0.07876738377017642</v>
       </c>
       <c r="T5">
-        <v>0.5057548776733757</v>
+        <v>0.5099949420401881</v>
       </c>
       <c r="U5">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y5">
-        <v>5.92403701955384</v>
+        <v>4.250855283494731</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07746628841936937</v>
+        <v>0.07765888057981418</v>
       </c>
       <c r="C6">
-        <v>8095.693110468945</v>
+        <v>7970.215337649737</v>
       </c>
       <c r="D6">
-        <v>8217.109110468946</v>
+        <v>8167.435337649737</v>
       </c>
       <c r="E6">
-        <v>-4936.983999999999</v>
+        <v>-4861.18</v>
       </c>
       <c r="F6">
-        <v>303.216</v>
+        <v>379.02</v>
       </c>
       <c r="G6">
         <v>181.8</v>
@@ -1767,45 +1767,45 @@
         <v>74.5</v>
       </c>
       <c r="M6">
-        <v>17.5258848</v>
+        <v>24.295182</v>
       </c>
       <c r="N6">
-        <v>56.9741152</v>
+        <v>50.204818</v>
       </c>
       <c r="O6">
-        <v>11.39482304</v>
+        <v>10.0409636</v>
       </c>
       <c r="P6">
-        <v>45.57929216</v>
+        <v>40.16385440000001</v>
       </c>
       <c r="Q6">
-        <v>70.07929215999999</v>
+        <v>64.66385440000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07876738377017642</v>
+        <v>0.07904724271559388</v>
       </c>
       <c r="T6">
-        <v>0.5099949420401881</v>
+        <v>0.5143242709199859</v>
       </c>
       <c r="U6">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.04624</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y6">
-        <v>4.250855283494731</v>
+        <v>3.066451611681691</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07765888057981418</v>
+        <v>0.07821147274025901</v>
       </c>
       <c r="C7">
-        <v>7970.215337649737</v>
+        <v>7755.162474301443</v>
       </c>
       <c r="D7">
-        <v>8167.435337649737</v>
+        <v>8028.186474301442</v>
       </c>
       <c r="E7">
-        <v>-4861.18</v>
+        <v>-4785.376</v>
       </c>
       <c r="F7">
-        <v>379.02</v>
+        <v>454.824</v>
       </c>
       <c r="G7">
         <v>181.8</v>
@@ -1849,45 +1849,45 @@
         <v>74.5</v>
       </c>
       <c r="M7">
-        <v>24.295182</v>
+        <v>34.4756592</v>
       </c>
       <c r="N7">
-        <v>50.204818</v>
+        <v>40.0243408</v>
       </c>
       <c r="O7">
-        <v>10.0409636</v>
+        <v>8.004868159999999</v>
       </c>
       <c r="P7">
-        <v>40.16385440000001</v>
+        <v>32.01947264</v>
       </c>
       <c r="Q7">
-        <v>64.66385440000001</v>
+        <v>56.51947264</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07904724271559388</v>
+        <v>0.07933305610665853</v>
       </c>
       <c r="T7">
-        <v>0.5143242709199859</v>
+        <v>0.5187457131802051</v>
       </c>
       <c r="U7">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.05128000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y7">
-        <v>3.066451611681691</v>
+        <v>2.160944902251499</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07821147274025901</v>
+        <v>0.07909126490070384</v>
       </c>
       <c r="C8">
-        <v>7755.162474301443</v>
+        <v>7467.196649157627</v>
       </c>
       <c r="D8">
-        <v>8028.186474301442</v>
+        <v>7816.024649157626</v>
       </c>
       <c r="E8">
-        <v>-4785.376</v>
+        <v>-4709.572</v>
       </c>
       <c r="F8">
-        <v>454.824</v>
+        <v>530.6279999999999</v>
       </c>
       <c r="G8">
         <v>181.8</v>
@@ -1931,45 +1931,45 @@
         <v>74.5</v>
       </c>
       <c r="M8">
-        <v>34.4756592</v>
+        <v>47.75651999999999</v>
       </c>
       <c r="N8">
-        <v>40.0243408</v>
+        <v>26.74348000000001</v>
       </c>
       <c r="O8">
-        <v>8.004868159999999</v>
+        <v>5.348696000000001</v>
       </c>
       <c r="P8">
-        <v>32.01947264</v>
+        <v>21.394784</v>
       </c>
       <c r="Q8">
-        <v>56.51947264</v>
+        <v>45.894784</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07933305610665853</v>
+        <v>0.07962501602226219</v>
       </c>
       <c r="T8">
-        <v>0.5187457131802051</v>
+        <v>0.5232622402202138</v>
       </c>
       <c r="U8">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y8">
-        <v>2.160944902251499</v>
+        <v>1.559996415149178</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07909126490070383</v>
+        <v>0.08339114309145287</v>
       </c>
       <c r="C9">
-        <v>7467.19664915763</v>
+        <v>6497.353490904117</v>
       </c>
       <c r="D9">
-        <v>7816.024649157629</v>
+        <v>6921.985490904117</v>
       </c>
       <c r="E9">
-        <v>-4709.572</v>
+        <v>-4633.768</v>
       </c>
       <c r="F9">
-        <v>530.628</v>
+        <v>606.432</v>
       </c>
       <c r="G9">
         <v>181.8</v>
@@ -2013,45 +2013,45 @@
         <v>74.5</v>
       </c>
       <c r="M9">
-        <v>47.75652</v>
+        <v>89.02421760000001</v>
       </c>
       <c r="N9">
-        <v>26.74348</v>
+        <v>-14.52421760000001</v>
       </c>
       <c r="O9">
-        <v>5.348696</v>
+        <v>-2.904843520000003</v>
       </c>
       <c r="P9">
-        <v>21.394784</v>
+        <v>-11.61937408000001</v>
       </c>
       <c r="Q9">
-        <v>45.894784</v>
+        <v>12.88062591999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07962501602226219</v>
+        <v>0.08001384627667481</v>
       </c>
       <c r="T9">
-        <v>0.5232622402202138</v>
+        <v>0.5292773205931378</v>
       </c>
       <c r="U9">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V9">
-        <v>0.2</v>
+        <v>0.1673701875926399</v>
       </c>
       <c r="W9">
-        <v>0.07199999999999999</v>
+        <v>0.1222300564614005</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y9">
-        <v>1.559996415149178</v>
+        <v>0.8368509379631996</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08339114309145287</v>
+        <v>0.0893760224986474</v>
       </c>
       <c r="C10">
-        <v>6497.353490904117</v>
+        <v>5470.860418199116</v>
       </c>
       <c r="D10">
-        <v>6921.985490904117</v>
+        <v>5971.296418199116</v>
       </c>
       <c r="E10">
-        <v>-4633.768</v>
+        <v>-4557.964</v>
       </c>
       <c r="F10">
-        <v>606.432</v>
+        <v>682.236</v>
       </c>
       <c r="G10">
         <v>181.8</v>
@@ -2095,45 +2095,45 @@
         <v>74.5</v>
       </c>
       <c r="M10">
-        <v>89.02421760000001</v>
+        <v>136.9929888</v>
       </c>
       <c r="N10">
-        <v>-14.52421760000001</v>
+        <v>-62.49298880000001</v>
       </c>
       <c r="O10">
-        <v>-2.904843520000003</v>
+        <v>-12.49859776</v>
       </c>
       <c r="P10">
-        <v>-11.61937408000001</v>
+        <v>-49.99439104</v>
       </c>
       <c r="Q10">
-        <v>12.88062591999999</v>
+        <v>-25.49439104</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08001384627667481</v>
+        <v>0.08051606371619269</v>
       </c>
       <c r="T10">
-        <v>0.5292773205931378</v>
+        <v>0.5370464646581939</v>
       </c>
       <c r="U10">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V10">
-        <v>0.1673701875926399</v>
+        <v>0.1087646902992455</v>
       </c>
       <c r="W10">
-        <v>0.1222300564614005</v>
+        <v>0.1789600501879115</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y10">
-        <v>0.8368509379631996</v>
+        <v>0.5438234514962272</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0893760224986474</v>
+        <v>0.09447237772703973</v>
       </c>
       <c r="C11">
-        <v>5470.860418199116</v>
+        <v>4769.817850816304</v>
       </c>
       <c r="D11">
-        <v>5971.296418199116</v>
+        <v>5346.057850816303</v>
       </c>
       <c r="E11">
-        <v>-4557.964</v>
+        <v>-4482.16</v>
       </c>
       <c r="F11">
-        <v>682.236</v>
+        <v>758.0399999999998</v>
       </c>
       <c r="G11">
         <v>181.8</v>
@@ -2177,45 +2177,45 @@
         <v>74.5</v>
       </c>
       <c r="M11">
-        <v>136.9929888</v>
+        <v>178.745832</v>
       </c>
       <c r="N11">
-        <v>-62.49298880000001</v>
+        <v>-104.245832</v>
       </c>
       <c r="O11">
-        <v>-12.49859776</v>
+        <v>-20.8491664</v>
       </c>
       <c r="P11">
-        <v>-49.99439104</v>
+        <v>-83.39666559999998</v>
       </c>
       <c r="Q11">
-        <v>-25.49439104</v>
+        <v>-58.89666559999998</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08051606371619269</v>
+        <v>0.08095330356680855</v>
       </c>
       <c r="T11">
-        <v>0.5370464646581939</v>
+        <v>0.5438104260882853</v>
       </c>
       <c r="U11">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.1087646902992455</v>
+        <v>0.08335858706904004</v>
       </c>
       <c r="W11">
-        <v>0.1789600501879115</v>
+        <v>0.2161440451691204</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y11">
-        <v>0.5438234514962272</v>
+        <v>0.4167929353452001</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09447237772703974</v>
+        <v>0.09637237772703974</v>
       </c>
       <c r="C12">
-        <v>4769.817850816302</v>
+        <v>4493.162904646136</v>
       </c>
       <c r="D12">
-        <v>5346.057850816302</v>
+        <v>5145.206904646136</v>
       </c>
       <c r="E12">
-        <v>-4482.16</v>
+        <v>-4406.356</v>
       </c>
       <c r="F12">
-        <v>758.04</v>
+        <v>833.8439999999999</v>
       </c>
       <c r="G12">
         <v>181.8</v>
@@ -2259,37 +2259,37 @@
         <v>74.5</v>
       </c>
       <c r="M12">
-        <v>178.745832</v>
+        <v>196.6204152</v>
       </c>
       <c r="N12">
-        <v>-104.245832</v>
+        <v>-122.1204152</v>
       </c>
       <c r="O12">
-        <v>-20.8491664</v>
+        <v>-24.42408304</v>
       </c>
       <c r="P12">
-        <v>-83.39666560000001</v>
+        <v>-97.69633216</v>
       </c>
       <c r="Q12">
-        <v>-58.89666560000001</v>
+        <v>-73.19633216</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08095330356680855</v>
+        <v>0.08134828450576145</v>
       </c>
       <c r="T12">
-        <v>0.5438104260882853</v>
+        <v>0.5499206555948952</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.08335858706904002</v>
+        <v>0.07578053369912729</v>
       </c>
       <c r="W12">
-        <v>0.2161440451691204</v>
+        <v>0.2179309501537458</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.4167929353452001</v>
+        <v>0.3789026684956365</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09637237772703974</v>
+        <v>0.09827237772703973</v>
       </c>
       <c r="C13">
-        <v>4493.162904646136</v>
+        <v>4231.05339416057</v>
       </c>
       <c r="D13">
-        <v>5145.206904646136</v>
+        <v>4958.90139416057</v>
       </c>
       <c r="E13">
-        <v>-4406.356</v>
+        <v>-4330.552</v>
       </c>
       <c r="F13">
-        <v>833.8439999999999</v>
+        <v>909.6479999999999</v>
       </c>
       <c r="G13">
         <v>181.8</v>
@@ -2341,37 +2341,37 @@
         <v>74.5</v>
       </c>
       <c r="M13">
-        <v>196.6204152</v>
+        <v>214.4949984</v>
       </c>
       <c r="N13">
-        <v>-122.1204152</v>
+        <v>-139.9949984</v>
       </c>
       <c r="O13">
-        <v>-24.42408304</v>
+        <v>-27.99899968</v>
       </c>
       <c r="P13">
-        <v>-97.69633216</v>
+        <v>-111.99599872</v>
       </c>
       <c r="Q13">
-        <v>-73.19633216</v>
+        <v>-87.49599871999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08134828450576145</v>
+        <v>0.08175224228423603</v>
       </c>
       <c r="T13">
-        <v>0.5499206555948952</v>
+        <v>0.5561697539539282</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.07578053369912729</v>
+        <v>0.06946548922420002</v>
       </c>
       <c r="W13">
-        <v>0.2179309501537458</v>
+        <v>0.2194200376409337</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.3789026684956365</v>
+        <v>0.3473274461210001</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09827237772703973</v>
+        <v>0.1001723777270397</v>
       </c>
       <c r="C14">
-        <v>4231.05339416057</v>
+        <v>3981.964482910136</v>
       </c>
       <c r="D14">
-        <v>4958.90139416057</v>
+        <v>4785.616482910136</v>
       </c>
       <c r="E14">
-        <v>-4330.552</v>
+        <v>-4254.748</v>
       </c>
       <c r="F14">
-        <v>909.6479999999999</v>
+        <v>985.452</v>
       </c>
       <c r="G14">
         <v>181.8</v>
@@ -2423,37 +2423,37 @@
         <v>74.5</v>
       </c>
       <c r="M14">
-        <v>214.4949984</v>
+        <v>232.3695816</v>
       </c>
       <c r="N14">
-        <v>-139.9949984</v>
+        <v>-157.8695816</v>
       </c>
       <c r="O14">
-        <v>-27.99899968</v>
+        <v>-31.57391632</v>
       </c>
       <c r="P14">
-        <v>-111.99599872</v>
+        <v>-126.29566528</v>
       </c>
       <c r="Q14">
-        <v>-87.49599871999999</v>
+        <v>-101.79566528</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08175224228423603</v>
+        <v>0.08216548644842264</v>
       </c>
       <c r="T14">
-        <v>0.5561697539539282</v>
+        <v>0.5625625097465021</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.06946548922420002</v>
+        <v>0.0641219900531077</v>
       </c>
       <c r="W14">
-        <v>0.2194200376409337</v>
+        <v>0.2206800347454772</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.3473274461210001</v>
+        <v>0.3206099502655385</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1001723777270397</v>
+        <v>0.1020723777270397</v>
       </c>
       <c r="C15">
-        <v>3981.964482910136</v>
+        <v>3744.577274863817</v>
       </c>
       <c r="D15">
-        <v>4785.616482910136</v>
+        <v>4624.033274863817</v>
       </c>
       <c r="E15">
-        <v>-4254.748</v>
+        <v>-4178.944</v>
       </c>
       <c r="F15">
-        <v>985.452</v>
+        <v>1061.256</v>
       </c>
       <c r="G15">
         <v>181.8</v>
@@ -2505,37 +2505,37 @@
         <v>74.5</v>
       </c>
       <c r="M15">
-        <v>232.3695816</v>
+        <v>250.2441648</v>
       </c>
       <c r="N15">
-        <v>-157.8695816</v>
+        <v>-175.7441648</v>
       </c>
       <c r="O15">
-        <v>-31.57391632</v>
+        <v>-35.14883296000001</v>
       </c>
       <c r="P15">
-        <v>-126.29566528</v>
+        <v>-140.59533184</v>
       </c>
       <c r="Q15">
-        <v>-101.79566528</v>
+        <v>-116.09533184</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08216548644842264</v>
+        <v>0.08258834094200895</v>
       </c>
       <c r="T15">
-        <v>0.5625625097465021</v>
+        <v>0.5691039342784382</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.0641219900531077</v>
+        <v>0.05954184790645716</v>
       </c>
       <c r="W15">
-        <v>0.2206800347454772</v>
+        <v>0.2217600322636574</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.3206099502655385</v>
+        <v>0.2977092395322858</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1020723777270397</v>
+        <v>0.1039723777270397</v>
       </c>
       <c r="C16">
-        <v>3744.577274863817</v>
+        <v>3517.745182743089</v>
       </c>
       <c r="D16">
-        <v>4624.033274863817</v>
+        <v>4473.005182743089</v>
       </c>
       <c r="E16">
-        <v>-4178.944</v>
+        <v>-4103.139999999999</v>
       </c>
       <c r="F16">
-        <v>1061.256</v>
+        <v>1137.06</v>
       </c>
       <c r="G16">
         <v>181.8</v>
@@ -2587,37 +2587,37 @@
         <v>74.5</v>
       </c>
       <c r="M16">
-        <v>250.2441648</v>
+        <v>268.118748</v>
       </c>
       <c r="N16">
-        <v>-175.7441648</v>
+        <v>-193.618748</v>
       </c>
       <c r="O16">
-        <v>-35.14883296000001</v>
+        <v>-38.72374960000001</v>
       </c>
       <c r="P16">
-        <v>-140.59533184</v>
+        <v>-154.8949984</v>
       </c>
       <c r="Q16">
-        <v>-116.09533184</v>
+        <v>-130.3949984</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08258834094200895</v>
+        <v>0.0830211449530914</v>
       </c>
       <c r="T16">
-        <v>0.5691039342784382</v>
+        <v>0.5757992746817139</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.05954184790645716</v>
+        <v>0.05557239137936001</v>
       </c>
       <c r="W16">
-        <v>0.2217600322636574</v>
+        <v>0.2226960301127469</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.2977092395322858</v>
+        <v>0.2778619568968</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1039723777270397</v>
+        <v>0.1058723777270397</v>
       </c>
       <c r="C17">
-        <v>3517.74518274309</v>
+        <v>3300.466678673535</v>
       </c>
       <c r="D17">
-        <v>4473.00518274309</v>
+        <v>4331.530678673535</v>
       </c>
       <c r="E17">
-        <v>-4103.139999999999</v>
+        <v>-4027.336</v>
       </c>
       <c r="F17">
-        <v>1137.06</v>
+        <v>1212.864</v>
       </c>
       <c r="G17">
         <v>181.8</v>
@@ -2669,37 +2669,37 @@
         <v>74.5</v>
       </c>
       <c r="M17">
-        <v>268.118748</v>
+        <v>285.9933312</v>
       </c>
       <c r="N17">
-        <v>-193.618748</v>
+        <v>-211.4933312</v>
       </c>
       <c r="O17">
-        <v>-38.7237496</v>
+        <v>-42.29866624</v>
       </c>
       <c r="P17">
-        <v>-154.8949984</v>
+        <v>-169.19466496</v>
       </c>
       <c r="Q17">
-        <v>-130.3949984</v>
+        <v>-144.69466496</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0830211449530914</v>
+        <v>0.0834642538215806</v>
       </c>
       <c r="T17">
-        <v>0.5757992746817139</v>
+        <v>0.5826540279517344</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.05557239137936002</v>
+        <v>0.05209911691815002</v>
       </c>
       <c r="W17">
-        <v>0.2226960301127469</v>
+        <v>0.2235150282307002</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.2778619568968</v>
+        <v>0.2604955845907501</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1058723777270397</v>
+        <v>0.1077723777270397</v>
       </c>
       <c r="C18">
-        <v>3300.466678673535</v>
+        <v>3091.86305743375</v>
       </c>
       <c r="D18">
-        <v>4331.530678673535</v>
+        <v>4198.73105743375</v>
       </c>
       <c r="E18">
-        <v>-4027.336</v>
+        <v>-3951.532</v>
       </c>
       <c r="F18">
-        <v>1212.864</v>
+        <v>1288.668</v>
       </c>
       <c r="G18">
         <v>181.8</v>
@@ -2751,37 +2751,37 @@
         <v>74.5</v>
       </c>
       <c r="M18">
-        <v>285.9933312</v>
+        <v>303.8679144</v>
       </c>
       <c r="N18">
-        <v>-211.4933312</v>
+        <v>-229.3679144</v>
       </c>
       <c r="O18">
-        <v>-42.29866624</v>
+        <v>-45.87358288000001</v>
       </c>
       <c r="P18">
-        <v>-169.19466496</v>
+        <v>-183.49433152</v>
       </c>
       <c r="Q18">
-        <v>-144.69466496</v>
+        <v>-158.99433152</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0834642538215806</v>
+        <v>0.08391804001220204</v>
       </c>
       <c r="T18">
-        <v>0.5826540279517344</v>
+        <v>0.5896739559993456</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.05209911691815002</v>
+        <v>0.04903446298178825</v>
       </c>
       <c r="W18">
-        <v>0.2235150282307002</v>
+        <v>0.2242376736288943</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.2604955845907501</v>
+        <v>0.2451723149089412</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1077723777270397</v>
+        <v>0.1096723777270397</v>
       </c>
       <c r="C19">
-        <v>3091.86305743375</v>
+        <v>2891.160168539766</v>
       </c>
       <c r="D19">
-        <v>4198.73105743375</v>
+        <v>4073.832168539766</v>
       </c>
       <c r="E19">
-        <v>-3951.532</v>
+        <v>-3875.728</v>
       </c>
       <c r="F19">
-        <v>1288.668</v>
+        <v>1364.472</v>
       </c>
       <c r="G19">
         <v>181.8</v>
@@ -2833,37 +2833,37 @@
         <v>74.5</v>
       </c>
       <c r="M19">
-        <v>303.8679144</v>
+        <v>321.7424976</v>
       </c>
       <c r="N19">
-        <v>-229.3679144</v>
+        <v>-247.2424976</v>
       </c>
       <c r="O19">
-        <v>-45.87358288000001</v>
+        <v>-49.44849952000001</v>
       </c>
       <c r="P19">
-        <v>-183.49433152</v>
+        <v>-197.79399808</v>
       </c>
       <c r="Q19">
-        <v>-158.99433152</v>
+        <v>-173.29399808</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08391804001220204</v>
+        <v>0.08438289415869231</v>
       </c>
       <c r="T19">
-        <v>0.5896739559993456</v>
+        <v>0.5968651018042156</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.04903446298178825</v>
+        <v>0.04631032614946667</v>
       </c>
       <c r="W19">
-        <v>0.2242376736288943</v>
+        <v>0.2248800250939558</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.2451723149089412</v>
+        <v>0.2315516307473333</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1096723777270397</v>
+        <v>0.1115723777270397</v>
       </c>
       <c r="C20">
-        <v>2891.160168539766</v>
+        <v>2697.673314616675</v>
       </c>
       <c r="D20">
-        <v>4073.832168539766</v>
+        <v>3956.149314616675</v>
       </c>
       <c r="E20">
-        <v>-3875.728</v>
+        <v>-3799.924</v>
       </c>
       <c r="F20">
-        <v>1364.472</v>
+        <v>1440.276</v>
       </c>
       <c r="G20">
         <v>181.8</v>
@@ -2915,37 +2915,37 @@
         <v>74.5</v>
       </c>
       <c r="M20">
-        <v>321.7424976</v>
+        <v>339.6170808</v>
       </c>
       <c r="N20">
-        <v>-247.2424976</v>
+        <v>-265.1170808</v>
       </c>
       <c r="O20">
-        <v>-49.44849952000001</v>
+        <v>-53.02341616</v>
       </c>
       <c r="P20">
-        <v>-197.79399808</v>
+        <v>-212.09366464</v>
       </c>
       <c r="Q20">
-        <v>-173.29399808</v>
+        <v>-187.59366464</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08438289415869231</v>
+        <v>0.08485922618534283</v>
       </c>
       <c r="T20">
-        <v>0.5968651018042156</v>
+        <v>0.6042338067647616</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.04631032614946667</v>
+        <v>0.04387294056265265</v>
       </c>
       <c r="W20">
-        <v>0.2248800250939558</v>
+        <v>0.2254547606153265</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.2315516307473333</v>
+        <v>0.2193647028132633</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1115723777270397</v>
+        <v>0.1134723777270397</v>
       </c>
       <c r="C21">
-        <v>2697.673314616675</v>
+        <v>2510.794693770773</v>
       </c>
       <c r="D21">
-        <v>3956.149314616675</v>
+        <v>3845.074693770773</v>
       </c>
       <c r="E21">
-        <v>-3799.924</v>
+        <v>-3724.12</v>
       </c>
       <c r="F21">
-        <v>1440.276</v>
+        <v>1516.08</v>
       </c>
       <c r="G21">
         <v>181.8</v>
@@ -2997,37 +2997,37 @@
         <v>74.5</v>
       </c>
       <c r="M21">
-        <v>339.6170808</v>
+        <v>357.491664</v>
       </c>
       <c r="N21">
-        <v>-265.1170808</v>
+        <v>-282.991664</v>
       </c>
       <c r="O21">
-        <v>-53.02341616</v>
+        <v>-56.59833280000001</v>
       </c>
       <c r="P21">
-        <v>-212.09366464</v>
+        <v>-226.3933312</v>
       </c>
       <c r="Q21">
-        <v>-187.59366464</v>
+        <v>-201.8933312</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08485922618534283</v>
+        <v>0.08534746651265962</v>
       </c>
       <c r="T21">
-        <v>0.6042338067647616</v>
+        <v>0.6117867293493211</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.04387294056265265</v>
+        <v>0.04167929353452001</v>
       </c>
       <c r="W21">
-        <v>0.2254547606153265</v>
+        <v>0.2259720225845602</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.2193647028132633</v>
+        <v>0.2083964676726</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1134723777270397</v>
+        <v>0.1153723777270397</v>
       </c>
       <c r="C22">
-        <v>2510.794693770773</v>
+        <v>2329.982899631158</v>
       </c>
       <c r="D22">
-        <v>3845.074693770773</v>
+        <v>3740.066899631158</v>
       </c>
       <c r="E22">
-        <v>-3724.12</v>
+        <v>-3648.316</v>
       </c>
       <c r="F22">
-        <v>1516.08</v>
+        <v>1591.884</v>
       </c>
       <c r="G22">
         <v>181.8</v>
@@ -3079,37 +3079,37 @@
         <v>74.5</v>
       </c>
       <c r="M22">
-        <v>357.491664</v>
+        <v>375.3662472</v>
       </c>
       <c r="N22">
-        <v>-282.991664</v>
+        <v>-300.8662472</v>
       </c>
       <c r="O22">
-        <v>-56.59833280000001</v>
+        <v>-60.17324944000001</v>
       </c>
       <c r="P22">
-        <v>-226.3933312</v>
+        <v>-240.69299776</v>
       </c>
       <c r="Q22">
-        <v>-201.8933312</v>
+        <v>-216.19299776</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08534746651265962</v>
+        <v>0.08584806735459202</v>
       </c>
       <c r="T22">
-        <v>0.6117867293493211</v>
+        <v>0.6195308651638695</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.04167929353452001</v>
+        <v>0.03969456527097143</v>
       </c>
       <c r="W22">
-        <v>0.2259720225845602</v>
+        <v>0.2264400215091049</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.2083964676726</v>
+        <v>0.1984728263548572</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1153723777270397</v>
+        <v>0.1172723777270397</v>
       </c>
       <c r="C23">
-        <v>2329.982899631158</v>
+        <v>2154.754096157594</v>
       </c>
       <c r="D23">
-        <v>3740.066899631158</v>
+        <v>3640.642096157594</v>
       </c>
       <c r="E23">
-        <v>-3648.316</v>
+        <v>-3572.512</v>
       </c>
       <c r="F23">
-        <v>1591.884</v>
+        <v>1667.688</v>
       </c>
       <c r="G23">
         <v>181.8</v>
@@ -3161,37 +3161,37 @@
         <v>74.5</v>
       </c>
       <c r="M23">
-        <v>375.3662472</v>
+        <v>393.2408304</v>
       </c>
       <c r="N23">
-        <v>-300.8662472</v>
+        <v>-318.7408304</v>
       </c>
       <c r="O23">
-        <v>-60.17324944</v>
+        <v>-63.74816608</v>
       </c>
       <c r="P23">
-        <v>-240.69299776</v>
+        <v>-254.99266432</v>
       </c>
       <c r="Q23">
-        <v>-216.19299776</v>
+        <v>-230.49266432</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08584806735459202</v>
+        <v>0.08636150411554833</v>
       </c>
       <c r="T23">
-        <v>0.6195308651638695</v>
+        <v>0.6274735685634062</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.03969456527097145</v>
+        <v>0.03789026684956365</v>
       </c>
       <c r="W23">
-        <v>0.2264400215091049</v>
+        <v>0.2268654750768729</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.1984728263548572</v>
+        <v>0.1894513342478182</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1172723777270397</v>
+        <v>0.1191723777270397</v>
       </c>
       <c r="C24">
-        <v>2154.754096157594</v>
+        <v>1984.67456363454</v>
       </c>
       <c r="D24">
-        <v>3640.642096157594</v>
+        <v>3546.366563634539</v>
       </c>
       <c r="E24">
-        <v>-3572.512</v>
+        <v>-3496.708</v>
       </c>
       <c r="F24">
-        <v>1667.688</v>
+        <v>1743.492</v>
       </c>
       <c r="G24">
         <v>181.8</v>
@@ -3243,37 +3243,37 @@
         <v>74.5</v>
       </c>
       <c r="M24">
-        <v>393.2408304</v>
+        <v>411.1154136</v>
       </c>
       <c r="N24">
-        <v>-318.7408304</v>
+        <v>-336.6154136</v>
       </c>
       <c r="O24">
-        <v>-63.74816608</v>
+        <v>-67.32308272</v>
       </c>
       <c r="P24">
-        <v>-254.99266432</v>
+        <v>-269.29233088</v>
       </c>
       <c r="Q24">
-        <v>-230.49266432</v>
+        <v>-244.79233088</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08636150411554833</v>
+        <v>0.08688827689626974</v>
       </c>
       <c r="T24">
-        <v>0.6274735685634062</v>
+        <v>0.6356225759473465</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.03789026684956365</v>
+        <v>0.03624286394306088</v>
       </c>
       <c r="W24">
-        <v>0.2268654750768729</v>
+        <v>0.2272539326822263</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.1894513342478182</v>
+        <v>0.1812143197153044</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1191723777270397</v>
+        <v>0.1210723777270397</v>
       </c>
       <c r="C25">
-        <v>1984.67456363454</v>
+        <v>1819.354373574223</v>
       </c>
       <c r="D25">
-        <v>3546.366563634539</v>
+        <v>3456.850373574222</v>
       </c>
       <c r="E25">
-        <v>-3496.708</v>
+        <v>-3420.904</v>
       </c>
       <c r="F25">
-        <v>1743.492</v>
+        <v>1819.296</v>
       </c>
       <c r="G25">
         <v>181.8</v>
@@ -3325,37 +3325,37 @@
         <v>74.5</v>
       </c>
       <c r="M25">
-        <v>411.1154136</v>
+        <v>428.9899968</v>
       </c>
       <c r="N25">
-        <v>-336.6154136</v>
+        <v>-354.4899968</v>
       </c>
       <c r="O25">
-        <v>-67.32308272</v>
+        <v>-70.89799936000001</v>
       </c>
       <c r="P25">
-        <v>-269.29233088</v>
+        <v>-283.59199744</v>
       </c>
       <c r="Q25">
-        <v>-244.79233088</v>
+        <v>-259.09199744</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08688827689626974</v>
+        <v>0.08742891211858908</v>
       </c>
       <c r="T25">
-        <v>0.6356225759473465</v>
+        <v>0.6439860308940222</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.03624286394306088</v>
+        <v>0.03473274461210001</v>
       </c>
       <c r="W25">
-        <v>0.2272539326822263</v>
+        <v>0.2276100188204668</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.1812143197153044</v>
+        <v>0.1736637230605</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1210723777270397</v>
+        <v>0.1229723777270397</v>
       </c>
       <c r="C26">
-        <v>1819.354373574223</v>
+        <v>1658.441997970944</v>
       </c>
       <c r="D26">
-        <v>3456.850373574222</v>
+        <v>3371.741997970944</v>
       </c>
       <c r="E26">
-        <v>-3420.904</v>
+        <v>-3345.1</v>
       </c>
       <c r="F26">
-        <v>1819.296</v>
+        <v>1895.1</v>
       </c>
       <c r="G26">
         <v>181.8</v>
@@ -3407,37 +3407,37 @@
         <v>74.5</v>
       </c>
       <c r="M26">
-        <v>428.9899968</v>
+        <v>446.86458</v>
       </c>
       <c r="N26">
-        <v>-354.4899968</v>
+        <v>-372.36458</v>
       </c>
       <c r="O26">
-        <v>-70.89799936</v>
+        <v>-74.472916</v>
       </c>
       <c r="P26">
-        <v>-283.59199744</v>
+        <v>-297.891664</v>
       </c>
       <c r="Q26">
-        <v>-259.09199744</v>
+        <v>-273.391664</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08742891211858908</v>
+        <v>0.08798396428017025</v>
       </c>
       <c r="T26">
-        <v>0.6439860308940222</v>
+        <v>0.6525725113059423</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.03473274461210001</v>
+        <v>0.03334343482761601</v>
       </c>
       <c r="W26">
-        <v>0.2276100188204668</v>
+        <v>0.2279376180676481</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.1736637230605</v>
+        <v>0.1667171741380801</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1229723777270397</v>
+        <v>0.1248723777270397</v>
       </c>
       <c r="C27">
-        <v>1658.441997970944</v>
+        <v>1501.619695748395</v>
       </c>
       <c r="D27">
-        <v>3371.741997970944</v>
+        <v>3290.723695748395</v>
       </c>
       <c r="E27">
-        <v>-3345.1</v>
+        <v>-3269.296</v>
       </c>
       <c r="F27">
-        <v>1895.1</v>
+        <v>1970.904</v>
       </c>
       <c r="G27">
         <v>181.8</v>
@@ -3489,37 +3489,37 @@
         <v>74.5</v>
       </c>
       <c r="M27">
-        <v>446.86458</v>
+        <v>464.7391632</v>
       </c>
       <c r="N27">
-        <v>-372.36458</v>
+        <v>-390.2391632</v>
       </c>
       <c r="O27">
-        <v>-74.472916</v>
+        <v>-78.04783264000001</v>
       </c>
       <c r="P27">
-        <v>-297.891664</v>
+        <v>-312.19133056</v>
       </c>
       <c r="Q27">
-        <v>-273.391664</v>
+        <v>-287.69133056</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08798396428017025</v>
+        <v>0.08855401785152392</v>
       </c>
       <c r="T27">
-        <v>0.6525725113059423</v>
+        <v>0.6613910587560228</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.03334343482761601</v>
+        <v>0.03206099502655385</v>
       </c>
       <c r="W27">
-        <v>0.2279376180676481</v>
+        <v>0.2282400173727386</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.1667171741380801</v>
+        <v>0.1603049751327693</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1248723777270397</v>
+        <v>0.1267723777270398</v>
       </c>
       <c r="C28">
-        <v>1501.619695748395</v>
+        <v>1348.599548743315</v>
       </c>
       <c r="D28">
-        <v>3290.723695748395</v>
+        <v>3213.507548743315</v>
       </c>
       <c r="E28">
-        <v>-3269.296</v>
+        <v>-3193.492</v>
       </c>
       <c r="F28">
-        <v>1970.904</v>
+        <v>2046.708</v>
       </c>
       <c r="G28">
         <v>181.8</v>
@@ -3571,37 +3571,37 @@
         <v>74.5</v>
       </c>
       <c r="M28">
-        <v>464.7391632</v>
+        <v>482.6137464</v>
       </c>
       <c r="N28">
-        <v>-390.2391632</v>
+        <v>-408.1137464</v>
       </c>
       <c r="O28">
-        <v>-78.04783264000001</v>
+        <v>-81.62274928000001</v>
       </c>
       <c r="P28">
-        <v>-312.19133056</v>
+        <v>-326.49099712</v>
       </c>
       <c r="Q28">
-        <v>-287.69133056</v>
+        <v>-301.99099712</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08855401785152392</v>
+        <v>0.08913968932894205</v>
       </c>
       <c r="T28">
-        <v>0.6613910587560228</v>
+        <v>0.6704512102458312</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.03206099502655385</v>
+        <v>0.03087355076631112</v>
       </c>
       <c r="W28">
-        <v>0.2282400173727386</v>
+        <v>0.2285200167293038</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.1603049751327693</v>
+        <v>0.1543677538315555</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1267723777270398</v>
+        <v>0.1286723777270397</v>
       </c>
       <c r="C29">
-        <v>1348.599548743315</v>
+        <v>1199.120042982846</v>
       </c>
       <c r="D29">
-        <v>3213.507548743315</v>
+        <v>3139.832042982846</v>
       </c>
       <c r="E29">
-        <v>-3193.492</v>
+        <v>-3117.688</v>
       </c>
       <c r="F29">
-        <v>2046.708</v>
+        <v>2122.512</v>
       </c>
       <c r="G29">
         <v>181.8</v>
@@ -3653,37 +3653,37 @@
         <v>74.5</v>
       </c>
       <c r="M29">
-        <v>482.6137464</v>
+        <v>500.4883296</v>
       </c>
       <c r="N29">
-        <v>-408.1137464</v>
+        <v>-425.9883296</v>
       </c>
       <c r="O29">
-        <v>-81.62274928000001</v>
+        <v>-85.19766592000002</v>
       </c>
       <c r="P29">
-        <v>-326.49099712</v>
+        <v>-340.79066368</v>
       </c>
       <c r="Q29">
-        <v>-301.99099712</v>
+        <v>-316.29066368</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08913968932894205</v>
+        <v>0.08974162945851069</v>
       </c>
       <c r="T29">
-        <v>0.6704512102458312</v>
+        <v>0.6797630326103566</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.03087355076631112</v>
+        <v>0.02977092395322858</v>
       </c>
       <c r="W29">
-        <v>0.2285200167293038</v>
+        <v>0.2287800161318287</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.1543677538315555</v>
+        <v>0.1488546197661429</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1286723777270397</v>
+        <v>0.1305723777270398</v>
       </c>
       <c r="C30">
-        <v>1199.120042982846</v>
+        <v>1052.943109704079</v>
       </c>
       <c r="D30">
-        <v>3139.832042982846</v>
+        <v>3069.459109704079</v>
       </c>
       <c r="E30">
-        <v>-3117.688</v>
+        <v>-3041.884</v>
       </c>
       <c r="F30">
-        <v>2122.512</v>
+        <v>2198.316</v>
       </c>
       <c r="G30">
         <v>181.8</v>
@@ -3735,37 +3735,37 @@
         <v>74.5</v>
       </c>
       <c r="M30">
-        <v>500.4883296</v>
+        <v>518.3629128000001</v>
       </c>
       <c r="N30">
-        <v>-425.9883296</v>
+        <v>-443.8629128000001</v>
       </c>
       <c r="O30">
-        <v>-85.19766592000002</v>
+        <v>-88.77258256000003</v>
       </c>
       <c r="P30">
-        <v>-340.79066368</v>
+        <v>-355.0903302400001</v>
       </c>
       <c r="Q30">
-        <v>-316.29066368</v>
+        <v>-330.5903302400001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08974162945851069</v>
+        <v>0.09036052564806718</v>
       </c>
       <c r="T30">
-        <v>0.6797630326103566</v>
+        <v>0.6893371598302209</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.02977092395322858</v>
+        <v>0.02874434036863449</v>
       </c>
       <c r="W30">
-        <v>0.2287800161318287</v>
+        <v>0.229022084541076</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1488546197661429</v>
+        <v>0.1437217018431725</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1305723777270397</v>
+        <v>0.1324723777270397</v>
       </c>
       <c r="C31">
-        <v>1052.94310970408</v>
+        <v>909.85155556769</v>
       </c>
       <c r="D31">
-        <v>3069.45910970408</v>
+        <v>3002.17155556769</v>
       </c>
       <c r="E31">
-        <v>-3041.884</v>
+        <v>-2966.08</v>
       </c>
       <c r="F31">
-        <v>2198.316</v>
+        <v>2274.12</v>
       </c>
       <c r="G31">
         <v>181.8</v>
@@ -3817,37 +3817,37 @@
         <v>74.5</v>
       </c>
       <c r="M31">
-        <v>518.3629128</v>
+        <v>536.237496</v>
       </c>
       <c r="N31">
-        <v>-443.8629128</v>
+        <v>-461.737496</v>
       </c>
       <c r="O31">
-        <v>-88.77258256</v>
+        <v>-92.3474992</v>
       </c>
       <c r="P31">
-        <v>-355.09033024</v>
+        <v>-369.3899967999999</v>
       </c>
       <c r="Q31">
-        <v>-330.59033024</v>
+        <v>-344.8899967999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09036052564806718</v>
+        <v>0.09099710458589672</v>
       </c>
       <c r="T31">
-        <v>0.6893371598302209</v>
+        <v>0.6991848335420812</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.02874434036863449</v>
+        <v>0.02778619568968001</v>
       </c>
       <c r="W31">
-        <v>0.229022084541076</v>
+        <v>0.2292480150563735</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1437217018431725</v>
+        <v>0.1389309784484001</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1324723777270397</v>
+        <v>0.1343723777270397</v>
       </c>
       <c r="C32">
-        <v>909.85155556769</v>
+        <v>769.6468236244036</v>
       </c>
       <c r="D32">
-        <v>3002.17155556769</v>
+        <v>2937.770823624403</v>
       </c>
       <c r="E32">
-        <v>-2966.08</v>
+        <v>-2890.276</v>
       </c>
       <c r="F32">
-        <v>2274.12</v>
+        <v>2349.924</v>
       </c>
       <c r="G32">
         <v>181.8</v>
@@ -3899,37 +3899,37 @@
         <v>74.5</v>
       </c>
       <c r="M32">
-        <v>536.237496</v>
+        <v>554.1120792</v>
       </c>
       <c r="N32">
-        <v>-461.737496</v>
+        <v>-479.6120792</v>
       </c>
       <c r="O32">
-        <v>-92.3474992</v>
+        <v>-95.92241584000001</v>
       </c>
       <c r="P32">
-        <v>-369.3899967999999</v>
+        <v>-383.6896633600001</v>
       </c>
       <c r="Q32">
-        <v>-344.8899967999999</v>
+        <v>-359.1896633600001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09099710458589672</v>
+        <v>0.09165213508714158</v>
       </c>
       <c r="T32">
-        <v>0.6991848335420812</v>
+        <v>0.7093179470716765</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.02778619568968001</v>
+        <v>0.02688986679646452</v>
       </c>
       <c r="W32">
-        <v>0.2292480150563735</v>
+        <v>0.2294593694093937</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1389309784484001</v>
+        <v>0.1344493339823226</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1343723777270397</v>
+        <v>0.1362723777270397</v>
       </c>
       <c r="C33">
-        <v>769.6468236244036</v>
+        <v>632.147036411573</v>
       </c>
       <c r="D33">
-        <v>2937.770823624403</v>
+        <v>2876.075036411573</v>
       </c>
       <c r="E33">
-        <v>-2890.276</v>
+        <v>-2814.472</v>
       </c>
       <c r="F33">
-        <v>2349.924</v>
+        <v>2425.728</v>
       </c>
       <c r="G33">
         <v>181.8</v>
@@ -3981,37 +3981,37 @@
         <v>74.5</v>
       </c>
       <c r="M33">
-        <v>554.1120792</v>
+        <v>571.9866624</v>
       </c>
       <c r="N33">
-        <v>-479.6120792</v>
+        <v>-497.4866624</v>
       </c>
       <c r="O33">
-        <v>-95.92241584000001</v>
+        <v>-99.49733248000001</v>
       </c>
       <c r="P33">
-        <v>-383.6896633600001</v>
+        <v>-397.98932992</v>
       </c>
       <c r="Q33">
-        <v>-359.1896633600001</v>
+        <v>-373.48932992</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09165213508714158</v>
+        <v>0.09232643119136424</v>
       </c>
       <c r="T33">
-        <v>0.7093179470716765</v>
+        <v>0.7197490933521423</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.02688986679646452</v>
+        <v>0.02604955845907501</v>
       </c>
       <c r="W33">
-        <v>0.2294593694093937</v>
+        <v>0.2296575141153501</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1344493339823226</v>
+        <v>0.1302477922953751</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1362723777270397</v>
+        <v>0.1381723777270397</v>
       </c>
       <c r="C34">
-        <v>632.147036411573</v>
+        <v>497.1852805580888</v>
       </c>
       <c r="D34">
-        <v>2876.075036411573</v>
+        <v>2816.917280558089</v>
       </c>
       <c r="E34">
-        <v>-2814.472</v>
+        <v>-2738.668</v>
       </c>
       <c r="F34">
-        <v>2425.728</v>
+        <v>2501.532</v>
       </c>
       <c r="G34">
         <v>181.8</v>
@@ -4063,37 +4063,37 @@
         <v>74.5</v>
       </c>
       <c r="M34">
-        <v>571.9866624</v>
+        <v>589.8612456000001</v>
       </c>
       <c r="N34">
-        <v>-497.4866624</v>
+        <v>-515.3612456000001</v>
       </c>
       <c r="O34">
-        <v>-99.49733248000001</v>
+        <v>-103.07224912</v>
       </c>
       <c r="P34">
-        <v>-397.98932992</v>
+        <v>-412.28899648</v>
       </c>
       <c r="Q34">
-        <v>-373.48932992</v>
+        <v>-387.78899648</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09232643119136424</v>
+        <v>0.09302085553750403</v>
       </c>
       <c r="T34">
-        <v>0.7197490933521423</v>
+        <v>0.7304916171335176</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.02604955845907501</v>
+        <v>0.0252601778997091</v>
       </c>
       <c r="W34">
-        <v>0.2296575141153501</v>
+        <v>0.2298436500512486</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1302477922953751</v>
+        <v>0.1263008894985455</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1381723777270397</v>
+        <v>0.1400723777270397</v>
       </c>
       <c r="C35">
-        <v>497.1852805580888</v>
+        <v>364.6080988255007</v>
       </c>
       <c r="D35">
-        <v>2816.917280558089</v>
+        <v>2760.144098825501</v>
       </c>
       <c r="E35">
-        <v>-2738.668</v>
+        <v>-2662.864</v>
       </c>
       <c r="F35">
-        <v>2501.532</v>
+        <v>2577.336</v>
       </c>
       <c r="G35">
         <v>181.8</v>
@@ -4145,37 +4145,37 @@
         <v>74.5</v>
       </c>
       <c r="M35">
-        <v>589.8612456000001</v>
+        <v>607.7358288</v>
       </c>
       <c r="N35">
-        <v>-515.3612456000001</v>
+        <v>-533.2358288</v>
       </c>
       <c r="O35">
-        <v>-103.07224912</v>
+        <v>-106.64716576</v>
       </c>
       <c r="P35">
-        <v>-412.28899648</v>
+        <v>-426.58866304</v>
       </c>
       <c r="Q35">
-        <v>-387.78899648</v>
+        <v>-402.08866304</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09302085553750403</v>
+        <v>0.09373632304564802</v>
       </c>
       <c r="T35">
-        <v>0.7304916171335176</v>
+        <v>0.7415596719385711</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.0252601778997091</v>
+        <v>0.02451723149089412</v>
       </c>
       <c r="W35">
-        <v>0.2298436500512486</v>
+        <v>0.2300188368144472</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1263008894985455</v>
+        <v>0.1225861574544707</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1400723777270397</v>
+        <v>0.1419723777270397</v>
       </c>
       <c r="C36">
-        <v>364.6080988255007</v>
+        <v>234.2741608982819</v>
       </c>
       <c r="D36">
-        <v>2760.144098825501</v>
+        <v>2705.614160898282</v>
       </c>
       <c r="E36">
-        <v>-2662.864</v>
+        <v>-2587.059999999999</v>
       </c>
       <c r="F36">
-        <v>2577.336</v>
+        <v>2653.14</v>
       </c>
       <c r="G36">
         <v>181.8</v>
@@ -4227,37 +4227,37 @@
         <v>74.5</v>
       </c>
       <c r="M36">
-        <v>607.7358288</v>
+        <v>625.6104120000001</v>
       </c>
       <c r="N36">
-        <v>-533.2358288</v>
+        <v>-551.1104120000001</v>
       </c>
       <c r="O36">
-        <v>-106.64716576</v>
+        <v>-110.2220824</v>
       </c>
       <c r="P36">
-        <v>-426.58866304</v>
+        <v>-440.8883296000001</v>
       </c>
       <c r="Q36">
-        <v>-402.08866304</v>
+        <v>-416.3883296000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09373632304564802</v>
+        <v>0.09447380493865801</v>
       </c>
       <c r="T36">
-        <v>0.7415596719385711</v>
+        <v>0.7529682822760875</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.02451723149089412</v>
+        <v>0.02381673916258286</v>
       </c>
       <c r="W36">
-        <v>0.2300188368144472</v>
+        <v>0.230184012905463</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1225861574544707</v>
+        <v>0.1190836958129143</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1419723777270397</v>
+        <v>0.1438723777270397</v>
       </c>
       <c r="C37">
-        <v>234.2741608982819</v>
+        <v>106.0530886823467</v>
       </c>
       <c r="D37">
-        <v>2705.614160898282</v>
+        <v>2653.197088682347</v>
       </c>
       <c r="E37">
-        <v>-2587.059999999999</v>
+        <v>-2511.255999999999</v>
       </c>
       <c r="F37">
-        <v>2653.14</v>
+        <v>2728.944</v>
       </c>
       <c r="G37">
         <v>181.8</v>
@@ -4309,37 +4309,37 @@
         <v>74.5</v>
       </c>
       <c r="M37">
-        <v>625.6104120000001</v>
+        <v>643.4849952000001</v>
       </c>
       <c r="N37">
-        <v>-551.1104120000001</v>
+        <v>-568.9849952000001</v>
       </c>
       <c r="O37">
-        <v>-110.2220824</v>
+        <v>-113.79699904</v>
       </c>
       <c r="P37">
-        <v>-440.8883296000001</v>
+        <v>-455.1879961600001</v>
       </c>
       <c r="Q37">
-        <v>-416.3883296000001</v>
+        <v>-430.6879961600001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09447380493865801</v>
+        <v>0.09523433314082452</v>
       </c>
       <c r="T37">
-        <v>0.7529682822760875</v>
+        <v>0.7647334116866513</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.02381673916258286</v>
+        <v>0.02315516307473334</v>
       </c>
       <c r="W37">
-        <v>0.230184012905463</v>
+        <v>0.2303400125469779</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1190836958129143</v>
+        <v>0.1157758153736667</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1438723777270397</v>
+        <v>0.1457723777270397</v>
       </c>
       <c r="C38">
-        <v>106.0530886823472</v>
+        <v>-20.17558444346651</v>
       </c>
       <c r="D38">
-        <v>2653.197088682347</v>
+        <v>2602.772415556533</v>
       </c>
       <c r="E38">
-        <v>-2511.256</v>
+        <v>-2435.452</v>
       </c>
       <c r="F38">
-        <v>2728.944</v>
+        <v>2804.748</v>
       </c>
       <c r="G38">
         <v>181.8</v>
@@ -4391,37 +4391,37 @@
         <v>74.5</v>
       </c>
       <c r="M38">
-        <v>643.4849952000001</v>
+        <v>661.3595784</v>
       </c>
       <c r="N38">
-        <v>-568.9849952000001</v>
+        <v>-586.8595784</v>
       </c>
       <c r="O38">
-        <v>-113.79699904</v>
+        <v>-117.37191568</v>
       </c>
       <c r="P38">
-        <v>-455.1879961600001</v>
+        <v>-469.48766272</v>
       </c>
       <c r="Q38">
-        <v>-430.6879961600001</v>
+        <v>-444.98766272</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09523433314082452</v>
+        <v>0.09601900509544078</v>
       </c>
       <c r="T38">
-        <v>0.7647334116866513</v>
+        <v>0.776872037268979</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.02315516307473334</v>
+        <v>0.02252934785649731</v>
       </c>
       <c r="W38">
-        <v>0.2303400125469779</v>
+        <v>0.2304875797754379</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1157758153736667</v>
+        <v>0.1126467392824865</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1457723777270397</v>
+        <v>0.1476723777270397</v>
       </c>
       <c r="C39">
-        <v>-20.17558444346651</v>
+        <v>-144.5233379112415</v>
       </c>
       <c r="D39">
-        <v>2602.772415556533</v>
+        <v>2554.228662088758</v>
       </c>
       <c r="E39">
-        <v>-2435.452</v>
+        <v>-2359.648</v>
       </c>
       <c r="F39">
-        <v>2804.748</v>
+        <v>2880.552</v>
       </c>
       <c r="G39">
         <v>181.8</v>
@@ -4473,37 +4473,37 @@
         <v>74.5</v>
       </c>
       <c r="M39">
-        <v>661.3595784</v>
+        <v>679.2341616</v>
       </c>
       <c r="N39">
-        <v>-586.8595784</v>
+        <v>-604.7341616</v>
       </c>
       <c r="O39">
-        <v>-117.37191568</v>
+        <v>-120.94683232</v>
       </c>
       <c r="P39">
-        <v>-469.48766272</v>
+        <v>-483.78732928</v>
       </c>
       <c r="Q39">
-        <v>-444.98766272</v>
+        <v>-459.28732928</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09601900509544078</v>
+        <v>0.09682898904859305</v>
       </c>
       <c r="T39">
-        <v>0.776872037268979</v>
+        <v>0.7894022314184787</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.02252934785649731</v>
+        <v>0.02193647028132632</v>
       </c>
       <c r="W39">
-        <v>0.2304875797754379</v>
+        <v>0.2306273803076633</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1126467392824865</v>
+        <v>0.1096823514066316</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1476723777270397</v>
+        <v>0.1495723777270397</v>
       </c>
       <c r="C40">
-        <v>-144.5233379112415</v>
+        <v>-267.0934867098554</v>
       </c>
       <c r="D40">
-        <v>2554.228662088758</v>
+        <v>2507.462513290144</v>
       </c>
       <c r="E40">
-        <v>-2359.648</v>
+        <v>-2283.844</v>
       </c>
       <c r="F40">
-        <v>2880.552</v>
+        <v>2956.356</v>
       </c>
       <c r="G40">
         <v>181.8</v>
@@ -4555,37 +4555,37 @@
         <v>74.5</v>
       </c>
       <c r="M40">
-        <v>679.2341616</v>
+        <v>697.1087448</v>
       </c>
       <c r="N40">
-        <v>-604.7341616</v>
+        <v>-622.6087448</v>
       </c>
       <c r="O40">
-        <v>-120.94683232</v>
+        <v>-124.52174896</v>
       </c>
       <c r="P40">
-        <v>-483.78732928</v>
+        <v>-498.08699584</v>
       </c>
       <c r="Q40">
-        <v>-459.28732928</v>
+        <v>-473.58699584</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09682898904859305</v>
+        <v>0.09766552985266835</v>
       </c>
       <c r="T40">
-        <v>0.7894022314184787</v>
+        <v>0.802343251605667</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.02193647028132632</v>
+        <v>0.02137399668436924</v>
       </c>
       <c r="W40">
-        <v>0.2306273803076633</v>
+        <v>0.2307600115818257</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1096823514066316</v>
+        <v>0.1068699834218462</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1495723777270397</v>
+        <v>0.1514723777270398</v>
       </c>
       <c r="C41">
-        <v>-267.0934867098554</v>
+        <v>-387.9819153725425</v>
       </c>
       <c r="D41">
-        <v>2507.462513290144</v>
+        <v>2462.378084627457</v>
       </c>
       <c r="E41">
-        <v>-2283.844</v>
+        <v>-2208.04</v>
       </c>
       <c r="F41">
-        <v>2956.356</v>
+        <v>3032.16</v>
       </c>
       <c r="G41">
         <v>181.8</v>
@@ -4637,37 +4637,37 @@
         <v>74.5</v>
       </c>
       <c r="M41">
-        <v>697.1087448</v>
+        <v>714.983328</v>
       </c>
       <c r="N41">
-        <v>-622.6087448</v>
+        <v>-640.483328</v>
       </c>
       <c r="O41">
-        <v>-124.52174896</v>
+        <v>-128.0966656</v>
       </c>
       <c r="P41">
-        <v>-498.08699584</v>
+        <v>-512.3866624</v>
       </c>
       <c r="Q41">
-        <v>-473.58699584</v>
+        <v>-487.8866624</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09766552985266835</v>
+        <v>0.09852995535021283</v>
       </c>
       <c r="T41">
-        <v>0.802343251605667</v>
+        <v>0.8157156391324281</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.02137399668436924</v>
+        <v>0.02083964676726001</v>
       </c>
       <c r="W41">
-        <v>0.2307600115818257</v>
+        <v>0.2308860112922801</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1068699834218462</v>
+        <v>0.1041982338363</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1514723777270398</v>
+        <v>0.1533723777270397</v>
       </c>
       <c r="C42">
-        <v>-387.9819153725425</v>
+        <v>-507.2777341800033</v>
       </c>
       <c r="D42">
-        <v>2462.378084627457</v>
+        <v>2418.886265819996</v>
       </c>
       <c r="E42">
-        <v>-2208.04</v>
+        <v>-2132.236</v>
       </c>
       <c r="F42">
-        <v>3032.16</v>
+        <v>3107.964</v>
       </c>
       <c r="G42">
         <v>181.8</v>
@@ -4719,37 +4719,37 @@
         <v>74.5</v>
       </c>
       <c r="M42">
-        <v>714.983328</v>
+        <v>732.8579112</v>
       </c>
       <c r="N42">
-        <v>-640.483328</v>
+        <v>-658.3579112</v>
       </c>
       <c r="O42">
-        <v>-128.0966656</v>
+        <v>-131.67158224</v>
       </c>
       <c r="P42">
-        <v>-512.3866624</v>
+        <v>-526.68632896</v>
       </c>
       <c r="Q42">
-        <v>-487.8866624</v>
+        <v>-502.18632896</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09852995535021283</v>
+        <v>0.09942368340699609</v>
       </c>
       <c r="T42">
-        <v>0.8157156391324281</v>
+        <v>0.8295413279312828</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.02083964676726001</v>
+        <v>0.02033136269976586</v>
       </c>
       <c r="W42">
-        <v>0.2308860112922801</v>
+        <v>0.2310058646753952</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1041982338363</v>
+        <v>0.1016568134988293</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1533723777270397</v>
+        <v>0.1552723777270397</v>
       </c>
       <c r="C43">
-        <v>-507.2777341800033</v>
+        <v>-625.0638670292365</v>
       </c>
       <c r="D43">
-        <v>2418.886265819996</v>
+        <v>2376.904132970763</v>
       </c>
       <c r="E43">
-        <v>-2132.236</v>
+        <v>-2056.432</v>
       </c>
       <c r="F43">
-        <v>3107.964</v>
+        <v>3183.768</v>
       </c>
       <c r="G43">
         <v>181.8</v>
@@ -4801,37 +4801,37 @@
         <v>74.5</v>
       </c>
       <c r="M43">
-        <v>732.8579112</v>
+        <v>750.7324944000001</v>
       </c>
       <c r="N43">
-        <v>-658.3579112</v>
+        <v>-676.2324944000001</v>
       </c>
       <c r="O43">
-        <v>-131.67158224</v>
+        <v>-135.24649888</v>
       </c>
       <c r="P43">
-        <v>-526.68632896</v>
+        <v>-540.9859955200001</v>
       </c>
       <c r="Q43">
-        <v>-502.18632896</v>
+        <v>-516.4859955200001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09942368340699609</v>
+        <v>0.100348229672634</v>
       </c>
       <c r="T43">
-        <v>0.8295413279312828</v>
+        <v>0.8438437646197532</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.02033136269976586</v>
+        <v>0.01984728263548572</v>
       </c>
       <c r="W43">
-        <v>0.2310058646753952</v>
+        <v>0.2311200107545525</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1016568134988293</v>
+        <v>0.0992364131774286</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1552723777270397</v>
+        <v>0.1571723777270397</v>
       </c>
       <c r="C44">
-        <v>-625.063867029236</v>
+        <v>-741.4175791285224</v>
       </c>
       <c r="D44">
-        <v>2376.904132970763</v>
+        <v>2336.354420871477</v>
       </c>
       <c r="E44">
-        <v>-2056.432</v>
+        <v>-1980.628</v>
       </c>
       <c r="F44">
-        <v>3183.768</v>
+        <v>3259.572</v>
       </c>
       <c r="G44">
         <v>181.8</v>
@@ -4883,37 +4883,37 @@
         <v>74.5</v>
       </c>
       <c r="M44">
-        <v>750.7324944</v>
+        <v>768.6070775999999</v>
       </c>
       <c r="N44">
-        <v>-676.2324944</v>
+        <v>-694.1070775999999</v>
       </c>
       <c r="O44">
-        <v>-135.24649888</v>
+        <v>-138.82141552</v>
       </c>
       <c r="P44">
-        <v>-540.98599552</v>
+        <v>-555.28566208</v>
       </c>
       <c r="Q44">
-        <v>-516.48599552</v>
+        <v>-530.78566208</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.100348229672634</v>
+        <v>0.1013052161581188</v>
       </c>
       <c r="T44">
-        <v>0.8438437646197532</v>
+        <v>0.8586480411920295</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.01984728263548572</v>
+        <v>0.01938571792303257</v>
       </c>
       <c r="W44">
-        <v>0.2311200107545525</v>
+        <v>0.2312288477137489</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.0992364131774286</v>
+        <v>0.09692858961516282</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1571723777270397</v>
+        <v>0.1590723777270397</v>
       </c>
       <c r="C45">
-        <v>-741.4175791285224</v>
+        <v>-856.4109515839414</v>
       </c>
       <c r="D45">
-        <v>2336.354420871477</v>
+        <v>2297.165048416058</v>
       </c>
       <c r="E45">
-        <v>-1980.628</v>
+        <v>-1904.824</v>
       </c>
       <c r="F45">
-        <v>3259.572</v>
+        <v>3335.376</v>
       </c>
       <c r="G45">
         <v>181.8</v>
@@ -4965,37 +4965,37 @@
         <v>74.5</v>
       </c>
       <c r="M45">
-        <v>768.6070775999999</v>
+        <v>786.4816608</v>
       </c>
       <c r="N45">
-        <v>-694.1070775999999</v>
+        <v>-711.9816608</v>
       </c>
       <c r="O45">
-        <v>-138.82141552</v>
+        <v>-142.39633216</v>
       </c>
       <c r="P45">
-        <v>-555.28566208</v>
+        <v>-569.5853286399999</v>
       </c>
       <c r="Q45">
-        <v>-530.78566208</v>
+        <v>-545.0853286399999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1013052161581188</v>
+        <v>0.1022963807323709</v>
       </c>
       <c r="T45">
-        <v>0.8586480411920295</v>
+        <v>0.8739810419276014</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.01938571792303257</v>
+        <v>0.01894513342478182</v>
       </c>
       <c r="W45">
-        <v>0.2312288477137489</v>
+        <v>0.2313327375384364</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.09692858961516282</v>
+        <v>0.09472566712390906</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1590723777270397</v>
+        <v>0.1609723777270398</v>
       </c>
       <c r="C46">
-        <v>-856.4109515839414</v>
+        <v>-970.1113090103263</v>
       </c>
       <c r="D46">
-        <v>2297.165048416058</v>
+        <v>2259.268690989673</v>
       </c>
       <c r="E46">
-        <v>-1904.824</v>
+        <v>-1829.02</v>
       </c>
       <c r="F46">
-        <v>3335.376</v>
+        <v>3411.18</v>
       </c>
       <c r="G46">
         <v>181.8</v>
@@ -5047,37 +5047,37 @@
         <v>74.5</v>
       </c>
       <c r="M46">
-        <v>786.4816608</v>
+        <v>804.3562439999999</v>
       </c>
       <c r="N46">
-        <v>-711.9816608</v>
+        <v>-729.8562439999999</v>
       </c>
       <c r="O46">
-        <v>-142.39633216</v>
+        <v>-145.9712488</v>
       </c>
       <c r="P46">
-        <v>-569.5853286399999</v>
+        <v>-583.8849951999999</v>
       </c>
       <c r="Q46">
-        <v>-545.0853286399999</v>
+        <v>-559.3849951999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1022963807323709</v>
+        <v>0.1033235876547776</v>
       </c>
       <c r="T46">
-        <v>0.8739810419276014</v>
+        <v>0.8898716063262851</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.01894513342478182</v>
+        <v>0.01852413045978667</v>
       </c>
       <c r="W46">
-        <v>0.2313327375384364</v>
+        <v>0.2314320100375823</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.09472566712390906</v>
+        <v>0.09262065229893335</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1609723777270398</v>
+        <v>0.1628723777270397</v>
       </c>
       <c r="C47">
-        <v>-970.1113090103263</v>
+        <v>-1082.581605503328</v>
       </c>
       <c r="D47">
-        <v>2259.268690989673</v>
+        <v>2222.602394496671</v>
       </c>
       <c r="E47">
-        <v>-1829.02</v>
+        <v>-1753.216</v>
       </c>
       <c r="F47">
-        <v>3411.18</v>
+        <v>3486.984</v>
       </c>
       <c r="G47">
         <v>181.8</v>
@@ -5129,37 +5129,37 @@
         <v>74.5</v>
       </c>
       <c r="M47">
-        <v>804.3562439999999</v>
+        <v>822.2308272</v>
       </c>
       <c r="N47">
-        <v>-729.8562439999999</v>
+        <v>-747.7308272</v>
       </c>
       <c r="O47">
-        <v>-145.9712488</v>
+        <v>-149.54616544</v>
       </c>
       <c r="P47">
-        <v>-583.8849951999999</v>
+        <v>-598.18466176</v>
       </c>
       <c r="Q47">
-        <v>-559.3849951999999</v>
+        <v>-573.68466176</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1033235876547776</v>
+        <v>0.1043888392780143</v>
       </c>
       <c r="T47">
-        <v>0.8898716063262851</v>
+        <v>0.9063507101471423</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.01852413045978667</v>
+        <v>0.01812143197153044</v>
       </c>
       <c r="W47">
-        <v>0.2314320100375823</v>
+        <v>0.2315269663411131</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.09262065229893335</v>
+        <v>0.09060715985765222</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1628723777270397</v>
+        <v>0.1647723777270397</v>
       </c>
       <c r="C48">
-        <v>-1082.581605503328</v>
+        <v>-1193.880773627416</v>
       </c>
       <c r="D48">
-        <v>2222.602394496671</v>
+        <v>2187.107226372584</v>
       </c>
       <c r="E48">
-        <v>-1753.216</v>
+        <v>-1677.412</v>
       </c>
       <c r="F48">
-        <v>3486.984</v>
+        <v>3562.788</v>
       </c>
       <c r="G48">
         <v>181.8</v>
@@ -5211,37 +5211,37 @@
         <v>74.5</v>
       </c>
       <c r="M48">
-        <v>822.2308272</v>
+        <v>840.1054104</v>
       </c>
       <c r="N48">
-        <v>-747.7308272</v>
+        <v>-765.6054104</v>
       </c>
       <c r="O48">
-        <v>-149.54616544</v>
+        <v>-153.12108208</v>
       </c>
       <c r="P48">
-        <v>-598.18466176</v>
+        <v>-612.48432832</v>
       </c>
       <c r="Q48">
-        <v>-573.68466176</v>
+        <v>-587.98432832</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1043888392780143</v>
+        <v>0.1054942890757126</v>
       </c>
       <c r="T48">
-        <v>0.9063507101471423</v>
+        <v>0.9234516669423714</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.01812143197153044</v>
+        <v>0.01773586958915745</v>
       </c>
       <c r="W48">
-        <v>0.2315269663411131</v>
+        <v>0.2316178819508767</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.09060715985765222</v>
+        <v>0.08867934794578725</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1647723777270397</v>
+        <v>0.1666723777270397</v>
       </c>
       <c r="C49">
-        <v>-1193.880773627416</v>
+        <v>-1304.064040489297</v>
       </c>
       <c r="D49">
-        <v>2187.107226372584</v>
+        <v>2152.727959510703</v>
       </c>
       <c r="E49">
-        <v>-1677.412</v>
+        <v>-1601.608</v>
       </c>
       <c r="F49">
-        <v>3562.788</v>
+        <v>3638.592</v>
       </c>
       <c r="G49">
         <v>181.8</v>
@@ -5293,37 +5293,37 @@
         <v>74.5</v>
       </c>
       <c r="M49">
-        <v>840.1054104</v>
+        <v>857.9799936000001</v>
       </c>
       <c r="N49">
-        <v>-765.6054104</v>
+        <v>-783.4799936000001</v>
       </c>
       <c r="O49">
-        <v>-153.12108208</v>
+        <v>-156.69599872</v>
       </c>
       <c r="P49">
-        <v>-612.48432832</v>
+        <v>-626.78399488</v>
       </c>
       <c r="Q49">
-        <v>-587.98432832</v>
+        <v>-602.28399488</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1054942890757126</v>
+        <v>0.1066422561733225</v>
       </c>
       <c r="T49">
-        <v>0.9234516669423714</v>
+        <v>0.9412103528451093</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.01773586958915745</v>
+        <v>0.01736637230605001</v>
       </c>
       <c r="W49">
-        <v>0.2316178819508767</v>
+        <v>0.2317050094102334</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.08867934794578725</v>
+        <v>0.08683186153025002</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1666723777270397</v>
+        <v>0.1685723777270398</v>
       </c>
       <c r="C50">
-        <v>-1304.064040489296</v>
+        <v>-1413.183214462419</v>
       </c>
       <c r="D50">
-        <v>2152.727959510703</v>
+        <v>2119.41278553758</v>
       </c>
       <c r="E50">
-        <v>-1601.608</v>
+        <v>-1525.804</v>
       </c>
       <c r="F50">
-        <v>3638.592</v>
+        <v>3714.396</v>
       </c>
       <c r="G50">
         <v>181.8</v>
@@ -5375,37 +5375,37 @@
         <v>74.5</v>
       </c>
       <c r="M50">
-        <v>857.9799935999999</v>
+        <v>875.8545768</v>
       </c>
       <c r="N50">
-        <v>-783.4799935999999</v>
+        <v>-801.3545768</v>
       </c>
       <c r="O50">
-        <v>-156.69599872</v>
+        <v>-160.27091536</v>
       </c>
       <c r="P50">
-        <v>-626.7839948799999</v>
+        <v>-641.08366144</v>
       </c>
       <c r="Q50">
-        <v>-602.2839948799999</v>
+        <v>-616.58366144</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1066422561733225</v>
+        <v>0.1078352415884857</v>
       </c>
       <c r="T50">
-        <v>0.9412103528451092</v>
+        <v>0.9596654578028565</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.01736637230605001</v>
+        <v>0.01701195654470205</v>
       </c>
       <c r="W50">
-        <v>0.2317050094102334</v>
+        <v>0.2317885806467593</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.08683186153025002</v>
+        <v>0.08505978272351022</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1685723777270398</v>
+        <v>0.1704723777270397</v>
       </c>
       <c r="C51">
-        <v>-1413.183214462419</v>
+        <v>-1521.286945693486</v>
       </c>
       <c r="D51">
-        <v>2119.41278553758</v>
+        <v>2087.113054306514</v>
       </c>
       <c r="E51">
-        <v>-1525.804</v>
+        <v>-1450</v>
       </c>
       <c r="F51">
-        <v>3714.396</v>
+        <v>3790.2</v>
       </c>
       <c r="G51">
         <v>181.8</v>
@@ -5457,37 +5457,37 @@
         <v>74.5</v>
       </c>
       <c r="M51">
-        <v>875.8545768</v>
+        <v>893.72916</v>
       </c>
       <c r="N51">
-        <v>-801.3545768</v>
+        <v>-819.22916</v>
       </c>
       <c r="O51">
-        <v>-160.27091536</v>
+        <v>-163.845832</v>
       </c>
       <c r="P51">
-        <v>-641.08366144</v>
+        <v>-655.383328</v>
       </c>
       <c r="Q51">
-        <v>-616.58366144</v>
+        <v>-630.883328</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1078352415884857</v>
+        <v>0.1090759464202554</v>
       </c>
       <c r="T51">
-        <v>0.9596654578028565</v>
+        <v>0.9788587669589136</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.01701195654470205</v>
+        <v>0.016671717413808</v>
       </c>
       <c r="W51">
-        <v>0.2317885806467593</v>
+        <v>0.2318688090338241</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.08505978272351022</v>
+        <v>0.08335858706903998</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1704723777270397</v>
+        <v>0.1723723777270397</v>
       </c>
       <c r="C52">
-        <v>-1521.286945693486</v>
+        <v>-1628.420963145906</v>
       </c>
       <c r="D52">
-        <v>2087.113054306514</v>
+        <v>2055.783036854094</v>
       </c>
       <c r="E52">
-        <v>-1450</v>
+        <v>-1374.196</v>
       </c>
       <c r="F52">
-        <v>3790.2</v>
+        <v>3866.004</v>
       </c>
       <c r="G52">
         <v>181.8</v>
@@ -5539,37 +5539,37 @@
         <v>74.5</v>
       </c>
       <c r="M52">
-        <v>893.72916</v>
+        <v>911.6037432000001</v>
       </c>
       <c r="N52">
-        <v>-819.22916</v>
+        <v>-837.1037432000001</v>
       </c>
       <c r="O52">
-        <v>-163.845832</v>
+        <v>-167.42074864</v>
       </c>
       <c r="P52">
-        <v>-655.383328</v>
+        <v>-669.68299456</v>
       </c>
       <c r="Q52">
-        <v>-630.883328</v>
+        <v>-645.18299456</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1090759464202554</v>
+        <v>0.1103672922655667</v>
       </c>
       <c r="T52">
-        <v>0.9788587669589136</v>
+        <v>0.9988354764886875</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.016671717413808</v>
+        <v>0.01634482099392942</v>
       </c>
       <c r="W52">
-        <v>0.2318688090338241</v>
+        <v>0.2319458912096314</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.08335858706903998</v>
+        <v>0.0817241049696471</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1723723777270397</v>
+        <v>0.1742723777270397</v>
       </c>
       <c r="C53">
-        <v>-1628.420963145906</v>
+        <v>-1734.628290609196</v>
       </c>
       <c r="D53">
-        <v>2055.783036854094</v>
+        <v>2025.379709390804</v>
       </c>
       <c r="E53">
-        <v>-1374.196</v>
+        <v>-1298.392</v>
       </c>
       <c r="F53">
-        <v>3866.004</v>
+        <v>3941.808</v>
       </c>
       <c r="G53">
         <v>181.8</v>
@@ -5621,37 +5621,37 @@
         <v>74.5</v>
       </c>
       <c r="M53">
-        <v>911.6037432000001</v>
+        <v>929.4783264</v>
       </c>
       <c r="N53">
-        <v>-837.1037432000001</v>
+        <v>-854.9783264</v>
       </c>
       <c r="O53">
-        <v>-167.42074864</v>
+        <v>-170.99566528</v>
       </c>
       <c r="P53">
-        <v>-669.68299456</v>
+        <v>-683.98266112</v>
       </c>
       <c r="Q53">
-        <v>-645.18299456</v>
+        <v>-659.48266112</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1103672922655667</v>
+        <v>0.111712444187766</v>
       </c>
       <c r="T53">
-        <v>0.9988354764886875</v>
+        <v>1.019644548915535</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.01634482099392942</v>
+        <v>0.01603049751327693</v>
       </c>
       <c r="W53">
-        <v>0.2319458912096314</v>
+        <v>0.2320200086863693</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.0817241049696471</v>
+        <v>0.0801524875663846</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1742723777270397</v>
+        <v>0.1761723777270397</v>
       </c>
       <c r="C54">
-        <v>-1734.628290609196</v>
+        <v>-1839.949443820128</v>
       </c>
       <c r="D54">
-        <v>2025.379709390804</v>
+        <v>1995.862556179872</v>
       </c>
       <c r="E54">
-        <v>-1298.392</v>
+        <v>-1222.588</v>
       </c>
       <c r="F54">
-        <v>3941.808</v>
+        <v>4017.612</v>
       </c>
       <c r="G54">
         <v>181.8</v>
@@ -5703,37 +5703,37 @@
         <v>74.5</v>
       </c>
       <c r="M54">
-        <v>929.4783264</v>
+        <v>947.3529096000001</v>
       </c>
       <c r="N54">
-        <v>-854.9783264</v>
+        <v>-872.8529096000001</v>
       </c>
       <c r="O54">
-        <v>-170.99566528</v>
+        <v>-174.57058192</v>
       </c>
       <c r="P54">
-        <v>-683.98266112</v>
+        <v>-698.2823276800001</v>
       </c>
       <c r="Q54">
-        <v>-659.48266112</v>
+        <v>-673.7823276800001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.111712444187766</v>
+        <v>0.113114836617293</v>
       </c>
       <c r="T54">
-        <v>1.019644548915535</v>
+        <v>1.041339113786078</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.01603049751327693</v>
+        <v>0.01572803529604529</v>
       </c>
       <c r="W54">
-        <v>0.2320200086863693</v>
+        <v>0.2320913292771925</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.0801524875663846</v>
+        <v>0.07864017648022648</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1761723777270397</v>
+        <v>0.1780723777270397</v>
       </c>
       <c r="C55">
-        <v>-1839.949443820128</v>
+        <v>-1944.422610594822</v>
       </c>
       <c r="D55">
-        <v>1995.862556179872</v>
+        <v>1967.193389405178</v>
       </c>
       <c r="E55">
-        <v>-1222.588</v>
+        <v>-1146.784</v>
       </c>
       <c r="F55">
-        <v>4017.612</v>
+        <v>4093.416</v>
       </c>
       <c r="G55">
         <v>181.8</v>
@@ -5785,37 +5785,37 @@
         <v>74.5</v>
       </c>
       <c r="M55">
-        <v>947.3529096000001</v>
+        <v>965.2274928000001</v>
       </c>
       <c r="N55">
-        <v>-872.8529096000001</v>
+        <v>-890.7274928000001</v>
       </c>
       <c r="O55">
-        <v>-174.57058192</v>
+        <v>-178.14549856</v>
       </c>
       <c r="P55">
-        <v>-698.2823276800001</v>
+        <v>-712.5819942400001</v>
       </c>
       <c r="Q55">
-        <v>-673.7823276800001</v>
+        <v>-688.0819942400001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.113114836617293</v>
+        <v>0.1145782026307124</v>
       </c>
       <c r="T55">
-        <v>1.041339113786078</v>
+        <v>1.063976920607515</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.01572803529604529</v>
+        <v>0.01543677538315556</v>
       </c>
       <c r="W55">
-        <v>0.2320913292771925</v>
+        <v>0.2321600083646519</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.07864017648022648</v>
+        <v>0.07718387691577777</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1780723777270397</v>
+        <v>0.1799723777270398</v>
       </c>
       <c r="C56">
-        <v>-1944.422610594822</v>
+        <v>-2048.083815655865</v>
       </c>
       <c r="D56">
-        <v>1967.193389405178</v>
+        <v>1939.336184344135</v>
       </c>
       <c r="E56">
-        <v>-1146.784</v>
+        <v>-1070.98</v>
       </c>
       <c r="F56">
-        <v>4093.416</v>
+        <v>4169.22</v>
       </c>
       <c r="G56">
         <v>181.8</v>
@@ -5867,37 +5867,37 @@
         <v>74.5</v>
       </c>
       <c r="M56">
-        <v>965.2274928000001</v>
+        <v>983.1020760000001</v>
       </c>
       <c r="N56">
-        <v>-890.7274928000001</v>
+        <v>-908.6020760000001</v>
       </c>
       <c r="O56">
-        <v>-178.14549856</v>
+        <v>-181.7204152</v>
       </c>
       <c r="P56">
-        <v>-712.5819942400001</v>
+        <v>-726.8816608000001</v>
       </c>
       <c r="Q56">
-        <v>-688.0819942400001</v>
+        <v>-702.3816608000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1145782026307124</v>
+        <v>0.1161066071336171</v>
       </c>
       <c r="T56">
-        <v>1.063976920607515</v>
+        <v>1.087620852176571</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.01543677538315556</v>
+        <v>0.01515610673982546</v>
       </c>
       <c r="W56">
-        <v>0.2321600083646519</v>
+        <v>0.2322261900307492</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.07718387691577777</v>
+        <v>0.07578053369912729</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1799723777270398</v>
+        <v>0.1818723777270397</v>
       </c>
       <c r="C57">
-        <v>-2048.083815655865</v>
+        <v>-2150.967071650387</v>
       </c>
       <c r="D57">
-        <v>1939.336184344135</v>
+        <v>1912.256928349613</v>
       </c>
       <c r="E57">
-        <v>-1070.98</v>
+        <v>-995.1759999999995</v>
       </c>
       <c r="F57">
-        <v>4169.22</v>
+        <v>4245.024</v>
       </c>
       <c r="G57">
         <v>181.8</v>
@@ -5949,37 +5949,37 @@
         <v>74.5</v>
       </c>
       <c r="M57">
-        <v>983.1020760000001</v>
+        <v>1000.9766592</v>
       </c>
       <c r="N57">
-        <v>-908.6020760000001</v>
+        <v>-926.4766592000001</v>
       </c>
       <c r="O57">
-        <v>-181.7204152</v>
+        <v>-185.29533184</v>
       </c>
       <c r="P57">
-        <v>-726.8816608000001</v>
+        <v>-741.1813273600001</v>
       </c>
       <c r="Q57">
-        <v>-702.3816608000001</v>
+        <v>-716.6813273600001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1161066071336171</v>
+        <v>0.117704484568472</v>
       </c>
       <c r="T57">
-        <v>1.087620852176571</v>
+        <v>1.112339507907856</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.01515610673982546</v>
+        <v>0.01488546197661429</v>
       </c>
       <c r="W57">
-        <v>0.2322261900307492</v>
+        <v>0.2322900080659143</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.07578053369912729</v>
+        <v>0.07442730988307145</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1818723777270397</v>
+        <v>0.1837723777270397</v>
       </c>
       <c r="C58">
-        <v>-2150.967071650387</v>
+        <v>-2253.104517690233</v>
       </c>
       <c r="D58">
-        <v>1912.256928349613</v>
+        <v>1885.923482309767</v>
       </c>
       <c r="E58">
-        <v>-995.1759999999995</v>
+        <v>-919.3719999999994</v>
       </c>
       <c r="F58">
-        <v>4245.024</v>
+        <v>4320.828</v>
       </c>
       <c r="G58">
         <v>181.8</v>
@@ -6031,37 +6031,37 @@
         <v>74.5</v>
       </c>
       <c r="M58">
-        <v>1000.9766592</v>
+        <v>1018.8512424</v>
       </c>
       <c r="N58">
-        <v>-926.4766592000001</v>
+        <v>-944.3512424000002</v>
       </c>
       <c r="O58">
-        <v>-185.29533184</v>
+        <v>-188.87024848</v>
       </c>
       <c r="P58">
-        <v>-741.1813273600001</v>
+        <v>-755.4809939200002</v>
       </c>
       <c r="Q58">
-        <v>-716.6813273600001</v>
+        <v>-730.9809939200002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.117704484568472</v>
+        <v>0.1193766818840179</v>
       </c>
       <c r="T58">
-        <v>1.112339507907856</v>
+        <v>1.138207868556876</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.01488546197661429</v>
+        <v>0.01462431352088421</v>
       </c>
       <c r="W58">
-        <v>0.2322900080659143</v>
+        <v>0.2323515868717755</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.07442730988307145</v>
+        <v>0.07312156760442101</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1837723777270397</v>
+        <v>0.1856723777270398</v>
       </c>
       <c r="C59">
-        <v>-2253.104517690233</v>
+        <v>-2354.526546600712</v>
       </c>
       <c r="D59">
-        <v>1885.923482309767</v>
+        <v>1860.305453399289</v>
       </c>
       <c r="E59">
-        <v>-919.3719999999994</v>
+        <v>-843.5679999999993</v>
       </c>
       <c r="F59">
-        <v>4320.828</v>
+        <v>4396.632000000001</v>
       </c>
       <c r="G59">
         <v>181.8</v>
@@ -6113,37 +6113,37 @@
         <v>74.5</v>
       </c>
       <c r="M59">
-        <v>1018.8512424</v>
+        <v>1036.7258256</v>
       </c>
       <c r="N59">
-        <v>-944.3512424000002</v>
+        <v>-962.2258256000002</v>
       </c>
       <c r="O59">
-        <v>-188.87024848</v>
+        <v>-192.4451651200001</v>
       </c>
       <c r="P59">
-        <v>-755.4809939200002</v>
+        <v>-769.7806604800002</v>
       </c>
       <c r="Q59">
-        <v>-730.9809939200002</v>
+        <v>-745.2806604800002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1193766818840179</v>
+        <v>0.1211285076431612</v>
       </c>
       <c r="T59">
-        <v>1.138207868556876</v>
+        <v>1.165308055903469</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01462431352088421</v>
+        <v>0.01437217018431724</v>
       </c>
       <c r="W59">
-        <v>0.2323515868717755</v>
+        <v>0.232411042270538</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.07312156760442101</v>
+        <v>0.07186085092158623</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1856723777270397</v>
+        <v>0.1875723777270397</v>
       </c>
       <c r="C60">
-        <v>-2354.526546600711</v>
+        <v>-2455.261921937195</v>
       </c>
       <c r="D60">
-        <v>1860.305453399289</v>
+        <v>1835.374078062805</v>
       </c>
       <c r="E60">
-        <v>-843.5680000000002</v>
+        <v>-767.7640000000001</v>
       </c>
       <c r="F60">
-        <v>4396.632</v>
+        <v>4472.436</v>
       </c>
       <c r="G60">
         <v>181.8</v>
@@ -6195,37 +6195,37 @@
         <v>74.5</v>
       </c>
       <c r="M60">
-        <v>1036.7258256</v>
+        <v>1054.6004088</v>
       </c>
       <c r="N60">
-        <v>-962.2258256</v>
+        <v>-980.1004088</v>
       </c>
       <c r="O60">
-        <v>-192.44516512</v>
+        <v>-196.02008176</v>
       </c>
       <c r="P60">
-        <v>-769.7806604800001</v>
+        <v>-784.0803270399999</v>
       </c>
       <c r="Q60">
-        <v>-745.2806604800001</v>
+        <v>-759.5803270399999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1211285076431612</v>
+        <v>0.1229657883173846</v>
       </c>
       <c r="T60">
-        <v>1.165308055903469</v>
+        <v>1.193730203608431</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.01437217018431725</v>
+        <v>0.01412857407949831</v>
       </c>
       <c r="W60">
-        <v>0.232411042270538</v>
+        <v>0.2324684822320543</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.07186085092158623</v>
+        <v>0.07064287039749151</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1875723777270397</v>
+        <v>0.1894723777270397</v>
       </c>
       <c r="C61">
-        <v>-2455.261921937195</v>
+        <v>-2555.337885716792</v>
       </c>
       <c r="D61">
-        <v>1835.374078062805</v>
+        <v>1811.102114283208</v>
       </c>
       <c r="E61">
-        <v>-767.7640000000001</v>
+        <v>-691.96</v>
       </c>
       <c r="F61">
-        <v>4472.436</v>
+        <v>4548.24</v>
       </c>
       <c r="G61">
         <v>181.8</v>
@@ -6277,37 +6277,37 @@
         <v>74.5</v>
       </c>
       <c r="M61">
-        <v>1054.6004088</v>
+        <v>1072.474992</v>
       </c>
       <c r="N61">
-        <v>-980.1004088</v>
+        <v>-997.9749919999999</v>
       </c>
       <c r="O61">
-        <v>-196.02008176</v>
+        <v>-199.5949984</v>
       </c>
       <c r="P61">
-        <v>-784.0803270399999</v>
+        <v>-798.3799935999999</v>
       </c>
       <c r="Q61">
-        <v>-759.5803270399999</v>
+        <v>-773.8799935999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1229657883173846</v>
+        <v>0.1248949330253192</v>
       </c>
       <c r="T61">
-        <v>1.193730203608431</v>
+        <v>1.223573458698642</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.01412857407949831</v>
+        <v>0.01389309784484001</v>
       </c>
       <c r="W61">
-        <v>0.2324684822320543</v>
+        <v>0.2325240075281867</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.07064287039749151</v>
+        <v>0.06946548922420004</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1894723777270397</v>
+        <v>0.1913723777270397</v>
       </c>
       <c r="C62">
-        <v>-2555.337885716792</v>
+        <v>-2654.78025771337</v>
       </c>
       <c r="D62">
-        <v>1811.102114283208</v>
+        <v>1787.46374228663</v>
       </c>
       <c r="E62">
-        <v>-691.96</v>
+        <v>-616.1559999999999</v>
       </c>
       <c r="F62">
-        <v>4548.24</v>
+        <v>4624.044</v>
       </c>
       <c r="G62">
         <v>181.8</v>
@@ -6359,37 +6359,37 @@
         <v>74.5</v>
       </c>
       <c r="M62">
-        <v>1072.474992</v>
+        <v>1090.3495752</v>
       </c>
       <c r="N62">
-        <v>-997.9749919999999</v>
+        <v>-1015.8495752</v>
       </c>
       <c r="O62">
-        <v>-199.5949984</v>
+        <v>-203.16991504</v>
       </c>
       <c r="P62">
-        <v>-798.3799935999999</v>
+        <v>-812.6796601600001</v>
       </c>
       <c r="Q62">
-        <v>-773.8799935999999</v>
+        <v>-788.1796601600001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1248949330253192</v>
+        <v>0.1269230082310966</v>
       </c>
       <c r="T62">
-        <v>1.223573458698642</v>
+        <v>1.254947137126812</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.01389309784484001</v>
+        <v>0.01366534214246558</v>
       </c>
       <c r="W62">
-        <v>0.2325240075281867</v>
+        <v>0.2325777123228066</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.06946548922420004</v>
+        <v>0.06832671071232788</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1913723777270397</v>
+        <v>0.1932723777270398</v>
       </c>
       <c r="C63">
-        <v>-2654.78025771337</v>
+        <v>-2753.613527076821</v>
       </c>
       <c r="D63">
-        <v>1787.46374228663</v>
+        <v>1764.434472923179</v>
       </c>
       <c r="E63">
-        <v>-616.1559999999999</v>
+        <v>-540.3519999999999</v>
       </c>
       <c r="F63">
-        <v>4624.044</v>
+        <v>4699.848</v>
       </c>
       <c r="G63">
         <v>181.8</v>
@@ -6441,37 +6441,37 @@
         <v>74.5</v>
       </c>
       <c r="M63">
-        <v>1090.3495752</v>
+        <v>1108.2241584</v>
       </c>
       <c r="N63">
-        <v>-1015.8495752</v>
+        <v>-1033.7241584</v>
       </c>
       <c r="O63">
-        <v>-203.16991504</v>
+        <v>-206.74483168</v>
       </c>
       <c r="P63">
-        <v>-812.6796601600001</v>
+        <v>-826.97932672</v>
       </c>
       <c r="Q63">
-        <v>-788.1796601600001</v>
+        <v>-802.47932672</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1269230082310966</v>
+        <v>0.1290578242371782</v>
       </c>
       <c r="T63">
-        <v>1.254947137126812</v>
+        <v>1.287972061788044</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01366534214246558</v>
+        <v>0.01344493339823226</v>
       </c>
       <c r="W63">
-        <v>0.2325777123228066</v>
+        <v>0.2326296847046968</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.06832671071232788</v>
+        <v>0.06722466699116125</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1932723777270398</v>
+        <v>0.1951723777270397</v>
       </c>
       <c r="C64">
-        <v>-2753.613527076821</v>
+        <v>-2851.860936960007</v>
       </c>
       <c r="D64">
-        <v>1764.434472923179</v>
+        <v>1741.991063039993</v>
       </c>
       <c r="E64">
-        <v>-540.3519999999999</v>
+        <v>-464.5479999999998</v>
       </c>
       <c r="F64">
-        <v>4699.848</v>
+        <v>4775.652</v>
       </c>
       <c r="G64">
         <v>181.8</v>
@@ -6523,37 +6523,37 @@
         <v>74.5</v>
       </c>
       <c r="M64">
-        <v>1108.2241584</v>
+        <v>1126.0987416</v>
       </c>
       <c r="N64">
-        <v>-1033.7241584</v>
+        <v>-1051.5987416</v>
       </c>
       <c r="O64">
-        <v>-206.74483168</v>
+        <v>-210.31974832</v>
       </c>
       <c r="P64">
-        <v>-826.97932672</v>
+        <v>-841.27899328</v>
       </c>
       <c r="Q64">
-        <v>-802.47932672</v>
+        <v>-816.77899328</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1290578242371782</v>
+        <v>0.1313080357030478</v>
       </c>
       <c r="T64">
-        <v>1.287972061788044</v>
+        <v>1.322782117512045</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01344493339823226</v>
+        <v>0.01323152175699048</v>
       </c>
       <c r="W64">
-        <v>0.2326296847046968</v>
+        <v>0.2326800071697017</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.06722466699116125</v>
+        <v>0.06615760878495236</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1951723777270397</v>
+        <v>0.1970723777270397</v>
       </c>
       <c r="C65">
-        <v>-2851.860936960007</v>
+        <v>-2949.544562768152</v>
       </c>
       <c r="D65">
-        <v>1741.991063039993</v>
+        <v>1720.111437231848</v>
       </c>
       <c r="E65">
-        <v>-464.5479999999998</v>
+        <v>-388.7439999999997</v>
       </c>
       <c r="F65">
-        <v>4775.652</v>
+        <v>4851.456</v>
       </c>
       <c r="G65">
         <v>181.8</v>
@@ -6605,37 +6605,37 @@
         <v>74.5</v>
       </c>
       <c r="M65">
-        <v>1126.0987416</v>
+        <v>1143.9733248</v>
       </c>
       <c r="N65">
-        <v>-1051.5987416</v>
+        <v>-1069.4733248</v>
       </c>
       <c r="O65">
-        <v>-210.31974832</v>
+        <v>-213.89466496</v>
       </c>
       <c r="P65">
-        <v>-841.27899328</v>
+        <v>-855.57865984</v>
       </c>
       <c r="Q65">
-        <v>-816.77899328</v>
+        <v>-831.07865984</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1313080357030478</v>
+        <v>0.1336832589170214</v>
       </c>
       <c r="T65">
-        <v>1.322782117512045</v>
+        <v>1.359526065220713</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01323152175699048</v>
+        <v>0.0130247792295375</v>
       </c>
       <c r="W65">
-        <v>0.2326800071697017</v>
+        <v>0.2327287570576751</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.06615760878495236</v>
+        <v>0.06512389614768754</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1970723777270397</v>
+        <v>0.1989723777270397</v>
       </c>
       <c r="C66">
-        <v>-2949.544562768152</v>
+        <v>-3046.68538458445</v>
       </c>
       <c r="D66">
-        <v>1720.111437231848</v>
+        <v>1698.77461541555</v>
       </c>
       <c r="E66">
-        <v>-388.7439999999997</v>
+        <v>-312.9399999999996</v>
       </c>
       <c r="F66">
-        <v>4851.456</v>
+        <v>4927.26</v>
       </c>
       <c r="G66">
         <v>181.8</v>
@@ -6687,37 +6687,37 @@
         <v>74.5</v>
       </c>
       <c r="M66">
-        <v>1143.9733248</v>
+        <v>1161.847908</v>
       </c>
       <c r="N66">
-        <v>-1069.4733248</v>
+        <v>-1087.347908</v>
       </c>
       <c r="O66">
-        <v>-213.89466496</v>
+        <v>-217.4695816000001</v>
       </c>
       <c r="P66">
-        <v>-855.57865984</v>
+        <v>-869.8783264000001</v>
       </c>
       <c r="Q66">
-        <v>-831.07865984</v>
+        <v>-845.3783264000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1336832589170214</v>
+        <v>0.1361942091717934</v>
       </c>
       <c r="T66">
-        <v>1.359526065220713</v>
+        <v>1.398369667084163</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0130247792295375</v>
+        <v>0.01282439801062154</v>
       </c>
       <c r="W66">
-        <v>0.2327287570576751</v>
+        <v>0.2327760069490954</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.06512389614768754</v>
+        <v>0.0641219900531077</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1989723777270397</v>
+        <v>0.2008723777270398</v>
       </c>
       <c r="C67">
-        <v>-3046.68538458445</v>
+        <v>-3143.303354271373</v>
       </c>
       <c r="D67">
-        <v>1698.77461541555</v>
+        <v>1677.960645728627</v>
       </c>
       <c r="E67">
-        <v>-312.9399999999996</v>
+        <v>-237.1359999999995</v>
       </c>
       <c r="F67">
-        <v>4927.26</v>
+        <v>5003.064</v>
       </c>
       <c r="G67">
         <v>181.8</v>
@@ -6769,37 +6769,37 @@
         <v>74.5</v>
       </c>
       <c r="M67">
-        <v>1161.847908</v>
+        <v>1179.7224912</v>
       </c>
       <c r="N67">
-        <v>-1087.347908</v>
+        <v>-1105.2224912</v>
       </c>
       <c r="O67">
-        <v>-217.4695816000001</v>
+        <v>-221.0444982400001</v>
       </c>
       <c r="P67">
-        <v>-869.8783264000001</v>
+        <v>-884.1779929600001</v>
       </c>
       <c r="Q67">
-        <v>-845.3783264000001</v>
+        <v>-859.6779929600001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1361942091717934</v>
+        <v>0.1388528623827285</v>
       </c>
       <c r="T67">
-        <v>1.398369667084163</v>
+        <v>1.439498186704285</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01282439801062154</v>
+        <v>0.01263008894985455</v>
       </c>
       <c r="W67">
-        <v>0.2327760069490954</v>
+        <v>0.2328218250256243</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.0641219900531077</v>
+        <v>0.06315044474927278</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2008723777270398</v>
+        <v>0.2027723777270397</v>
       </c>
       <c r="C68">
-        <v>-3143.303354271373</v>
+        <v>-3239.417457698793</v>
       </c>
       <c r="D68">
-        <v>1677.960645728627</v>
+        <v>1657.650542301207</v>
       </c>
       <c r="E68">
-        <v>-237.1359999999995</v>
+        <v>-161.3319999999994</v>
       </c>
       <c r="F68">
-        <v>5003.064</v>
+        <v>5078.868</v>
       </c>
       <c r="G68">
         <v>181.8</v>
@@ -6851,37 +6851,37 @@
         <v>74.5</v>
       </c>
       <c r="M68">
-        <v>1179.7224912</v>
+        <v>1197.5970744</v>
       </c>
       <c r="N68">
-        <v>-1105.2224912</v>
+        <v>-1123.0970744</v>
       </c>
       <c r="O68">
-        <v>-221.0444982400001</v>
+        <v>-224.61941488</v>
       </c>
       <c r="P68">
-        <v>-884.1779929600001</v>
+        <v>-898.4776595200001</v>
       </c>
       <c r="Q68">
-        <v>-859.6779929600001</v>
+        <v>-873.9776595200001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1388528623827285</v>
+        <v>0.1416726460912961</v>
       </c>
       <c r="T68">
-        <v>1.439498186704285</v>
+        <v>1.483119343877142</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01263008894985455</v>
+        <v>0.01244158015955821</v>
       </c>
       <c r="W68">
-        <v>0.2328218250256243</v>
+        <v>0.2328662753983762</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.06315044474927278</v>
+        <v>0.06220790079779104</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2027723777270397</v>
+        <v>0.2046723777270398</v>
       </c>
       <c r="C69">
-        <v>-3239.417457698793</v>
+        <v>-3335.045772506895</v>
       </c>
       <c r="D69">
-        <v>1657.650542301207</v>
+        <v>1637.826227493106</v>
       </c>
       <c r="E69">
-        <v>-161.3319999999994</v>
+        <v>-85.52799999999934</v>
       </c>
       <c r="F69">
-        <v>5078.868</v>
+        <v>5154.672</v>
       </c>
       <c r="G69">
         <v>181.8</v>
@@ -6933,37 +6933,37 @@
         <v>74.5</v>
       </c>
       <c r="M69">
-        <v>1197.5970744</v>
+        <v>1215.4716576</v>
       </c>
       <c r="N69">
-        <v>-1123.0970744</v>
+        <v>-1140.9716576</v>
       </c>
       <c r="O69">
-        <v>-224.61941488</v>
+        <v>-228.19433152</v>
       </c>
       <c r="P69">
-        <v>-898.4776595200001</v>
+        <v>-912.7773260800001</v>
       </c>
       <c r="Q69">
-        <v>-873.9776595200001</v>
+        <v>-888.2773260800001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1416726460912961</v>
+        <v>0.1446686662816491</v>
       </c>
       <c r="T69">
-        <v>1.483119343877142</v>
+        <v>1.529466823373303</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01244158015955821</v>
+        <v>0.01225861574544706</v>
       </c>
       <c r="W69">
-        <v>0.2328662753983762</v>
+        <v>0.2329094184072236</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.06220790079779104</v>
+        <v>0.06129307872723533</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2046723777270398</v>
+        <v>0.2065723777270397</v>
       </c>
       <c r="C70">
-        <v>-3335.045772506895</v>
+        <v>-3430.205521773229</v>
       </c>
       <c r="D70">
-        <v>1637.826227493106</v>
+        <v>1618.470478226772</v>
       </c>
       <c r="E70">
-        <v>-85.52799999999934</v>
+        <v>-9.723999999999251</v>
       </c>
       <c r="F70">
-        <v>5154.672</v>
+        <v>5230.476000000001</v>
       </c>
       <c r="G70">
         <v>181.8</v>
@@ -7015,37 +7015,37 @@
         <v>74.5</v>
       </c>
       <c r="M70">
-        <v>1215.4716576</v>
+        <v>1233.3462408</v>
       </c>
       <c r="N70">
-        <v>-1140.9716576</v>
+        <v>-1158.8462408</v>
       </c>
       <c r="O70">
-        <v>-228.19433152</v>
+        <v>-231.7692481600001</v>
       </c>
       <c r="P70">
-        <v>-912.7773260800001</v>
+        <v>-927.0769926400002</v>
       </c>
       <c r="Q70">
-        <v>-888.2773260800001</v>
+        <v>-902.5769926400002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1446686662816491</v>
+        <v>0.1478579780971861</v>
       </c>
       <c r="T70">
-        <v>1.529466823373303</v>
+        <v>1.578804462836958</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01225861574544706</v>
+        <v>0.01208095464768696</v>
       </c>
       <c r="W70">
-        <v>0.2329094184072236</v>
+        <v>0.2329513108940754</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.06129307872723533</v>
+        <v>0.06040477323843474</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2065723777270397</v>
+        <v>0.2084723777270397</v>
       </c>
       <c r="C71">
-        <v>-3430.205521773229</v>
+        <v>-3524.913123918829</v>
       </c>
       <c r="D71">
-        <v>1618.470478226772</v>
+        <v>1599.566876081171</v>
       </c>
       <c r="E71">
-        <v>-9.723999999999251</v>
+        <v>66.08000000000084</v>
       </c>
       <c r="F71">
-        <v>5230.476000000001</v>
+        <v>5306.280000000001</v>
       </c>
       <c r="G71">
         <v>181.8</v>
@@ -7097,37 +7097,37 @@
         <v>74.5</v>
       </c>
       <c r="M71">
-        <v>1233.3462408</v>
+        <v>1251.220824</v>
       </c>
       <c r="N71">
-        <v>-1158.8462408</v>
+        <v>-1176.720824</v>
       </c>
       <c r="O71">
-        <v>-231.7692481600001</v>
+        <v>-235.3441648</v>
       </c>
       <c r="P71">
-        <v>-927.0769926400002</v>
+        <v>-941.3766592000002</v>
       </c>
       <c r="Q71">
-        <v>-902.5769926400002</v>
+        <v>-916.8766592000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1478579780971861</v>
+        <v>0.1512599107004257</v>
       </c>
       <c r="T71">
-        <v>1.578804462836958</v>
+        <v>1.631431278264856</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01208095464768696</v>
+        <v>0.01190836958129143</v>
       </c>
       <c r="W71">
-        <v>0.2329513108940754</v>
+        <v>0.2329920064527315</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.06040477323843474</v>
+        <v>0.05954184790645711</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2084723777270397</v>
+        <v>0.2103723777270398</v>
       </c>
       <c r="C72">
-        <v>-3524.913123918829</v>
+        <v>-3619.184239157299</v>
       </c>
       <c r="D72">
-        <v>1599.566876081171</v>
+        <v>1581.099760842701</v>
       </c>
       <c r="E72">
-        <v>66.08000000000084</v>
+        <v>141.8840000000009</v>
       </c>
       <c r="F72">
-        <v>5306.280000000001</v>
+        <v>5382.084000000001</v>
       </c>
       <c r="G72">
         <v>181.8</v>
@@ -7179,37 +7179,37 @@
         <v>74.5</v>
       </c>
       <c r="M72">
-        <v>1251.220824</v>
+        <v>1269.0954072</v>
       </c>
       <c r="N72">
-        <v>-1176.720824</v>
+        <v>-1194.5954072</v>
       </c>
       <c r="O72">
-        <v>-235.3441648</v>
+        <v>-238.91908144</v>
       </c>
       <c r="P72">
-        <v>-941.3766592000002</v>
+        <v>-955.6763257600002</v>
       </c>
       <c r="Q72">
-        <v>-916.8766592000002</v>
+        <v>-931.1763257600002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1512599107004257</v>
+        <v>0.154896459345268</v>
       </c>
       <c r="T72">
-        <v>1.631431278264856</v>
+        <v>1.687687529239507</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01190836958129143</v>
+        <v>0.01174064606606197</v>
       </c>
       <c r="W72">
-        <v>0.2329920064527315</v>
+        <v>0.2330315556576226</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.05954184790645711</v>
+        <v>0.05870323033030989</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2103723777270397</v>
+        <v>0.2122723777270397</v>
       </c>
       <c r="C73">
-        <v>-3619.184239157298</v>
+        <v>-3713.03381276307</v>
       </c>
       <c r="D73">
-        <v>1581.099760842701</v>
+        <v>1563.05418723693</v>
       </c>
       <c r="E73">
-        <v>141.884</v>
+        <v>217.6880000000001</v>
       </c>
       <c r="F73">
-        <v>5382.084</v>
+        <v>5457.888</v>
       </c>
       <c r="G73">
         <v>181.8</v>
@@ -7261,37 +7261,37 @@
         <v>74.5</v>
       </c>
       <c r="M73">
-        <v>1269.0954072</v>
+        <v>1286.9699904</v>
       </c>
       <c r="N73">
-        <v>-1194.5954072</v>
+        <v>-1212.4699904</v>
       </c>
       <c r="O73">
-        <v>-238.91908144</v>
+        <v>-242.49399808</v>
       </c>
       <c r="P73">
-        <v>-955.6763257599999</v>
+        <v>-969.9759923200002</v>
       </c>
       <c r="Q73">
-        <v>-931.1763257599999</v>
+        <v>-945.4759923200002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1548964593452679</v>
+        <v>0.1587927614647417</v>
       </c>
       <c r="T73">
-        <v>1.687687529239506</v>
+        <v>1.747962083855203</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01174064606606198</v>
+        <v>0.01157758153736667</v>
       </c>
       <c r="W73">
-        <v>0.2330315556576226</v>
+        <v>0.2330700062734889</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.05870323033030989</v>
+        <v>0.05788790768683338</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2122723777270397</v>
+        <v>0.2141723777270397</v>
       </c>
       <c r="C74">
-        <v>-3713.03381276307</v>
+        <v>-3806.476115410103</v>
       </c>
       <c r="D74">
-        <v>1563.05418723693</v>
+        <v>1545.415884589897</v>
       </c>
       <c r="E74">
-        <v>217.6880000000001</v>
+        <v>293.4920000000002</v>
       </c>
       <c r="F74">
-        <v>5457.888</v>
+        <v>5533.692</v>
       </c>
       <c r="G74">
         <v>181.8</v>
@@ -7343,37 +7343,37 @@
         <v>74.5</v>
       </c>
       <c r="M74">
-        <v>1286.9699904</v>
+        <v>1304.8445736</v>
       </c>
       <c r="N74">
-        <v>-1212.4699904</v>
+        <v>-1230.3445736</v>
       </c>
       <c r="O74">
-        <v>-242.49399808</v>
+        <v>-246.06891472</v>
       </c>
       <c r="P74">
-        <v>-969.9759923200002</v>
+        <v>-984.27565888</v>
       </c>
       <c r="Q74">
-        <v>-945.4759923200002</v>
+        <v>-959.77565888</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1587927614647417</v>
+        <v>0.1629776785560285</v>
       </c>
       <c r="T74">
-        <v>1.747962083855203</v>
+        <v>1.812701420294284</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01157758153736667</v>
+        <v>0.01141898453000548</v>
       </c>
       <c r="W74">
-        <v>0.2330700062734889</v>
+        <v>0.2331074034478247</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.05788790768683338</v>
+        <v>0.05709492265002736</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2141723777270397</v>
+        <v>0.2160723777270397</v>
       </c>
       <c r="C75">
-        <v>-3806.476115410103</v>
+        <v>-3899.524780809843</v>
       </c>
       <c r="D75">
-        <v>1545.415884589897</v>
+        <v>1528.171219190157</v>
       </c>
       <c r="E75">
-        <v>293.4920000000002</v>
+        <v>369.2960000000003</v>
       </c>
       <c r="F75">
-        <v>5533.692</v>
+        <v>5609.496</v>
       </c>
       <c r="G75">
         <v>181.8</v>
@@ -7425,37 +7425,37 @@
         <v>74.5</v>
       </c>
       <c r="M75">
-        <v>1304.8445736</v>
+        <v>1322.7191568</v>
       </c>
       <c r="N75">
-        <v>-1230.3445736</v>
+        <v>-1248.2191568</v>
       </c>
       <c r="O75">
-        <v>-246.06891472</v>
+        <v>-249.64383136</v>
       </c>
       <c r="P75">
-        <v>-984.27565888</v>
+        <v>-998.57532544</v>
       </c>
       <c r="Q75">
-        <v>-959.77565888</v>
+        <v>-974.07532544</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1629776785560285</v>
+        <v>0.167484512346645</v>
       </c>
       <c r="T75">
-        <v>1.812701420294284</v>
+        <v>1.882420705690218</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01141898453000548</v>
+        <v>0.01126467392824865</v>
       </c>
       <c r="W75">
-        <v>0.2331074034478247</v>
+        <v>0.233143789887719</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.05709492265002736</v>
+        <v>0.05632336964124329</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2160723777270397</v>
+        <v>0.2179723777270398</v>
       </c>
       <c r="C76">
-        <v>-3899.524780809843</v>
+        <v>-3992.192840857061</v>
       </c>
       <c r="D76">
-        <v>1528.171219190157</v>
+        <v>1511.307159142938</v>
       </c>
       <c r="E76">
-        <v>369.2960000000003</v>
+        <v>445.0999999999995</v>
       </c>
       <c r="F76">
-        <v>5609.496</v>
+        <v>5685.299999999999</v>
       </c>
       <c r="G76">
         <v>181.8</v>
@@ -7507,37 +7507,37 @@
         <v>74.5</v>
       </c>
       <c r="M76">
-        <v>1322.7191568</v>
+        <v>1340.59374</v>
       </c>
       <c r="N76">
-        <v>-1248.2191568</v>
+        <v>-1266.09374</v>
       </c>
       <c r="O76">
-        <v>-249.64383136</v>
+        <v>-253.218748</v>
       </c>
       <c r="P76">
-        <v>-998.57532544</v>
+        <v>-1012.874992</v>
       </c>
       <c r="Q76">
-        <v>-974.07532544</v>
+        <v>-988.3749919999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.167484512346645</v>
+        <v>0.1723518928405108</v>
       </c>
       <c r="T76">
-        <v>1.882420705690218</v>
+        <v>1.957717533917827</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01126467392824865</v>
+        <v>0.011114478275872</v>
       </c>
       <c r="W76">
-        <v>0.233143789887719</v>
+        <v>0.2331792060225494</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.05632336964124329</v>
+        <v>0.05557239137935999</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2179723777270398</v>
+        <v>0.2198723777270398</v>
       </c>
       <c r="C77">
-        <v>-3992.192840857061</v>
+        <v>-4084.492758474011</v>
       </c>
       <c r="D77">
-        <v>1511.307159142938</v>
+        <v>1494.811241525989</v>
       </c>
       <c r="E77">
-        <v>445.0999999999995</v>
+        <v>520.9039999999995</v>
       </c>
       <c r="F77">
-        <v>5685.299999999999</v>
+        <v>5761.103999999999</v>
       </c>
       <c r="G77">
         <v>181.8</v>
@@ -7589,37 +7589,37 @@
         <v>74.5</v>
       </c>
       <c r="M77">
-        <v>1340.59374</v>
+        <v>1358.4683232</v>
       </c>
       <c r="N77">
-        <v>-1266.09374</v>
+        <v>-1283.9683232</v>
       </c>
       <c r="O77">
-        <v>-253.218748</v>
+        <v>-256.79366464</v>
       </c>
       <c r="P77">
-        <v>-1012.874992</v>
+        <v>-1027.17465856</v>
       </c>
       <c r="Q77">
-        <v>-988.3749919999998</v>
+        <v>-1002.67465856</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1723518928405108</v>
+        <v>0.1776248883755321</v>
       </c>
       <c r="T77">
-        <v>1.957717533917827</v>
+        <v>2.03928909783107</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.011114478275872</v>
+        <v>0.01096823514066316</v>
       </c>
       <c r="W77">
-        <v>0.2331792060225494</v>
+        <v>0.2332136901538316</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.05557239137935999</v>
+        <v>0.05484117570331581</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2198723777270398</v>
+        <v>0.2217723777270397</v>
       </c>
       <c r="C78">
-        <v>-4084.492758474011</v>
+        <v>-4176.436458326818</v>
       </c>
       <c r="D78">
-        <v>1494.811241525989</v>
+        <v>1478.671541673182</v>
       </c>
       <c r="E78">
-        <v>520.9039999999995</v>
+        <v>596.7079999999996</v>
       </c>
       <c r="F78">
-        <v>5761.103999999999</v>
+        <v>5836.907999999999</v>
       </c>
       <c r="G78">
         <v>181.8</v>
@@ -7671,37 +7671,37 @@
         <v>74.5</v>
       </c>
       <c r="M78">
-        <v>1358.4683232</v>
+        <v>1376.3429064</v>
       </c>
       <c r="N78">
-        <v>-1283.9683232</v>
+        <v>-1301.8429064</v>
       </c>
       <c r="O78">
-        <v>-256.79366464</v>
+        <v>-260.36858128</v>
       </c>
       <c r="P78">
-        <v>-1027.17465856</v>
+        <v>-1041.47432512</v>
       </c>
       <c r="Q78">
-        <v>-1002.67465856</v>
+        <v>-1016.97432512</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1776248883755321</v>
+        <v>0.1833564052614247</v>
       </c>
       <c r="T78">
-        <v>2.03928909783107</v>
+        <v>2.127953841215029</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01096823514066316</v>
+        <v>0.01082579052844676</v>
       </c>
       <c r="W78">
-        <v>0.2332136901538316</v>
+        <v>0.2332472785933923</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.05484117570331581</v>
+        <v>0.05412895264223383</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2217723777270397</v>
+        <v>0.2236723777270397</v>
       </c>
       <c r="C79">
-        <v>-4176.436458326818</v>
+        <v>-4268.035355573261</v>
       </c>
       <c r="D79">
-        <v>1478.671541673182</v>
+        <v>1462.876644426739</v>
       </c>
       <c r="E79">
-        <v>596.7079999999996</v>
+        <v>672.5119999999997</v>
       </c>
       <c r="F79">
-        <v>5836.907999999999</v>
+        <v>5912.712</v>
       </c>
       <c r="G79">
         <v>181.8</v>
@@ -7753,37 +7753,37 @@
         <v>74.5</v>
       </c>
       <c r="M79">
-        <v>1376.3429064</v>
+        <v>1394.2174896</v>
       </c>
       <c r="N79">
-        <v>-1301.8429064</v>
+        <v>-1319.7174896</v>
       </c>
       <c r="O79">
-        <v>-260.36858128</v>
+        <v>-263.94349792</v>
       </c>
       <c r="P79">
-        <v>-1041.47432512</v>
+        <v>-1055.77399168</v>
       </c>
       <c r="Q79">
-        <v>-1016.97432512</v>
+        <v>-1031.27399168</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1833564052614247</v>
+        <v>0.1896089691369441</v>
       </c>
       <c r="T79">
-        <v>2.127953841215029</v>
+        <v>2.224679015815713</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01082579052844676</v>
+        <v>0.01068699834218462</v>
       </c>
       <c r="W79">
-        <v>0.2332472785933923</v>
+        <v>0.2332800057909129</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.05412895264223383</v>
+        <v>0.05343499171092314</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2236723777270397</v>
+        <v>0.2255723777270398</v>
       </c>
       <c r="C80">
-        <v>-4268.035355573261</v>
+        <v>-4359.300382787525</v>
       </c>
       <c r="D80">
-        <v>1462.876644426739</v>
+        <v>1447.415617212474</v>
       </c>
       <c r="E80">
-        <v>672.5119999999997</v>
+        <v>748.3159999999998</v>
       </c>
       <c r="F80">
-        <v>5912.712</v>
+        <v>5988.516</v>
       </c>
       <c r="G80">
         <v>181.8</v>
@@ -7835,37 +7835,37 @@
         <v>74.5</v>
       </c>
       <c r="M80">
-        <v>1394.2174896</v>
+        <v>1412.0920728</v>
       </c>
       <c r="N80">
-        <v>-1319.7174896</v>
+        <v>-1337.5920728</v>
       </c>
       <c r="O80">
-        <v>-263.94349792</v>
+        <v>-267.51841456</v>
       </c>
       <c r="P80">
-        <v>-1055.77399168</v>
+        <v>-1070.07365824</v>
       </c>
       <c r="Q80">
-        <v>-1031.27399168</v>
+        <v>-1045.57365824</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1896089691369441</v>
+        <v>0.1964570152863224</v>
       </c>
       <c r="T80">
-        <v>2.224679015815713</v>
+        <v>2.330616111806938</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01068699834218462</v>
+        <v>0.01055171988215697</v>
       </c>
       <c r="W80">
-        <v>0.2332800057909129</v>
+        <v>0.2333119044517874</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.05343499171092314</v>
+        <v>0.05275859941078487</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2255723777270398</v>
+        <v>0.2274723777270398</v>
       </c>
       <c r="C81">
-        <v>-4359.300382787525</v>
+        <v>-4450.24201519544</v>
       </c>
       <c r="D81">
-        <v>1447.415617212474</v>
+        <v>1432.27798480456</v>
       </c>
       <c r="E81">
-        <v>748.3159999999998</v>
+        <v>824.1199999999999</v>
       </c>
       <c r="F81">
-        <v>5988.516</v>
+        <v>6064.32</v>
       </c>
       <c r="G81">
         <v>181.8</v>
@@ -7917,37 +7917,37 @@
         <v>74.5</v>
       </c>
       <c r="M81">
-        <v>1412.0920728</v>
+        <v>1429.966656</v>
       </c>
       <c r="N81">
-        <v>-1337.5920728</v>
+        <v>-1355.466656</v>
       </c>
       <c r="O81">
-        <v>-267.51841456</v>
+        <v>-271.0933312</v>
       </c>
       <c r="P81">
-        <v>-1070.07365824</v>
+        <v>-1084.3733248</v>
       </c>
       <c r="Q81">
-        <v>-1045.57365824</v>
+        <v>-1059.8733248</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1964570152863224</v>
+        <v>0.2039898660506385</v>
       </c>
       <c r="T81">
-        <v>2.330616111806938</v>
+        <v>2.447146917397284</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01055171988215697</v>
+        <v>0.01041982338363</v>
       </c>
       <c r="W81">
-        <v>0.2333119044517874</v>
+        <v>0.2333430056461401</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.05275859941078487</v>
+        <v>0.05209911691815006</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2274723777270398</v>
+        <v>0.2293723777270398</v>
       </c>
       <c r="C82">
-        <v>-4450.24201519544</v>
+        <v>-4540.870294342573</v>
       </c>
       <c r="D82">
-        <v>1432.27798480456</v>
+        <v>1417.453705657426</v>
       </c>
       <c r="E82">
-        <v>824.1199999999999</v>
+        <v>899.924</v>
       </c>
       <c r="F82">
-        <v>6064.32</v>
+        <v>6140.124</v>
       </c>
       <c r="G82">
         <v>181.8</v>
@@ -7999,37 +7999,37 @@
         <v>74.5</v>
       </c>
       <c r="M82">
-        <v>1429.966656</v>
+        <v>1447.8412392</v>
       </c>
       <c r="N82">
-        <v>-1355.466656</v>
+        <v>-1373.3412392</v>
       </c>
       <c r="O82">
-        <v>-271.0933312</v>
+        <v>-274.66824784</v>
       </c>
       <c r="P82">
-        <v>-1084.3733248</v>
+        <v>-1098.67299136</v>
       </c>
       <c r="Q82">
-        <v>-1059.8733248</v>
+        <v>-1074.17299136</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2039898660506385</v>
+        <v>0.2123156484743564</v>
       </c>
       <c r="T82">
-        <v>2.447146917397284</v>
+        <v>2.57594412357609</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01041982338363</v>
+        <v>0.01029118358877037</v>
       </c>
       <c r="W82">
-        <v>0.2333430056461401</v>
+        <v>0.233373338909768</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.05209911691815006</v>
+        <v>0.05145591794385185</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2293723777270398</v>
+        <v>0.2312723777270397</v>
       </c>
       <c r="C83">
-        <v>-4540.870294342573</v>
+        <v>-4631.194850307585</v>
       </c>
       <c r="D83">
-        <v>1417.453705657426</v>
+        <v>1402.933149692415</v>
       </c>
       <c r="E83">
-        <v>899.924</v>
+        <v>975.7280000000001</v>
       </c>
       <c r="F83">
-        <v>6140.124</v>
+        <v>6215.928</v>
       </c>
       <c r="G83">
         <v>181.8</v>
@@ -8081,37 +8081,37 @@
         <v>74.5</v>
       </c>
       <c r="M83">
-        <v>1447.8412392</v>
+        <v>1465.7158224</v>
       </c>
       <c r="N83">
-        <v>-1373.3412392</v>
+        <v>-1391.2158224</v>
       </c>
       <c r="O83">
-        <v>-274.66824784</v>
+        <v>-278.24316448</v>
       </c>
       <c r="P83">
-        <v>-1098.67299136</v>
+        <v>-1112.97265792</v>
       </c>
       <c r="Q83">
-        <v>-1074.17299136</v>
+        <v>-1088.47265792</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2123156484743564</v>
+        <v>0.2215665178340428</v>
       </c>
       <c r="T83">
-        <v>2.57594412357609</v>
+        <v>2.719052130441427</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01029118358877037</v>
+        <v>0.01016568134988293</v>
       </c>
       <c r="W83">
-        <v>0.233373338909768</v>
+        <v>0.2334029323376976</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.05145591794385185</v>
+        <v>0.05082840674941469</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2312723777270397</v>
+        <v>0.2331723777270397</v>
       </c>
       <c r="C84">
-        <v>-4631.194850307585</v>
+        <v>-4721.224922564077</v>
       </c>
       <c r="D84">
-        <v>1402.933149692415</v>
+        <v>1388.707077435923</v>
       </c>
       <c r="E84">
-        <v>975.7280000000001</v>
+        <v>1051.532</v>
       </c>
       <c r="F84">
-        <v>6215.928</v>
+        <v>6291.732</v>
       </c>
       <c r="G84">
         <v>181.8</v>
@@ -8163,37 +8163,37 @@
         <v>74.5</v>
       </c>
       <c r="M84">
-        <v>1465.7158224</v>
+        <v>1483.5904056</v>
       </c>
       <c r="N84">
-        <v>-1391.2158224</v>
+        <v>-1409.0904056</v>
       </c>
       <c r="O84">
-        <v>-278.24316448</v>
+        <v>-281.81808112</v>
       </c>
       <c r="P84">
-        <v>-1112.97265792</v>
+        <v>-1127.27232448</v>
       </c>
       <c r="Q84">
-        <v>-1088.47265792</v>
+        <v>-1102.77232448</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2215665178340428</v>
+        <v>0.2319057247654571</v>
       </c>
       <c r="T84">
-        <v>2.719052130441427</v>
+        <v>2.87899637340857</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01016568134988293</v>
+        <v>0.01004320326133012</v>
       </c>
       <c r="W84">
-        <v>0.2334029323376976</v>
+        <v>0.2334318126709784</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.05082840674941469</v>
+        <v>0.05021601630665062</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2331723777270397</v>
+        <v>0.2350723777270398</v>
       </c>
       <c r="C85">
-        <v>-4721.224922564077</v>
+        <v>-4810.969379585933</v>
       </c>
       <c r="D85">
-        <v>1388.707077435923</v>
+        <v>1374.766620414068</v>
       </c>
       <c r="E85">
-        <v>1051.532</v>
+        <v>1127.336</v>
       </c>
       <c r="F85">
-        <v>6291.732</v>
+        <v>6367.536</v>
       </c>
       <c r="G85">
         <v>181.8</v>
@@ -8245,37 +8245,37 @@
         <v>74.5</v>
       </c>
       <c r="M85">
-        <v>1483.5904056</v>
+        <v>1501.4649888</v>
       </c>
       <c r="N85">
-        <v>-1409.0904056</v>
+        <v>-1426.9649888</v>
       </c>
       <c r="O85">
-        <v>-281.81808112</v>
+        <v>-285.39299776</v>
       </c>
       <c r="P85">
-        <v>-1127.27232448</v>
+        <v>-1141.57199104</v>
       </c>
       <c r="Q85">
-        <v>-1102.77232448</v>
+        <v>-1117.07199104</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2319057247654571</v>
+        <v>0.2435373325632982</v>
       </c>
       <c r="T85">
-        <v>2.87899637340857</v>
+        <v>3.058933646746607</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01004320326133012</v>
+        <v>0.009923641317742858</v>
       </c>
       <c r="W85">
-        <v>0.2334318126709784</v>
+        <v>0.2334600053772763</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.05021601630665062</v>
+        <v>0.0496182065887143</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2350723777270398</v>
+        <v>0.2369723777270397</v>
       </c>
       <c r="C86">
-        <v>-4810.969379585931</v>
+        <v>-4900.43673728354</v>
       </c>
       <c r="D86">
-        <v>1374.766620414068</v>
+        <v>1361.10326271646</v>
       </c>
       <c r="E86">
-        <v>1127.335999999999</v>
+        <v>1203.139999999999</v>
       </c>
       <c r="F86">
-        <v>6367.535999999999</v>
+        <v>6443.339999999999</v>
       </c>
       <c r="G86">
         <v>181.8</v>
@@ -8327,37 +8327,37 @@
         <v>74.5</v>
       </c>
       <c r="M86">
-        <v>1501.4649888</v>
+        <v>1519.339572</v>
       </c>
       <c r="N86">
-        <v>-1426.9649888</v>
+        <v>-1444.839572</v>
       </c>
       <c r="O86">
-        <v>-285.39299776</v>
+        <v>-288.9679144</v>
       </c>
       <c r="P86">
-        <v>-1141.57199104</v>
+        <v>-1155.8716576</v>
       </c>
       <c r="Q86">
-        <v>-1117.07199104</v>
+        <v>-1131.3716576</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2435373325632981</v>
+        <v>0.2567198214008513</v>
       </c>
       <c r="T86">
-        <v>3.058933646746605</v>
+        <v>3.262862556529711</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.009923641317742862</v>
+        <v>0.00980689259635765</v>
       </c>
       <c r="W86">
-        <v>0.2334600053772763</v>
+        <v>0.2334875347257789</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.0496182065887143</v>
+        <v>0.04903446298178826</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2369723777270397</v>
+        <v>0.2388723777270397</v>
       </c>
       <c r="C87">
-        <v>-4900.43673728354</v>
+        <v>-4989.635176351449</v>
       </c>
       <c r="D87">
-        <v>1361.10326271646</v>
+        <v>1347.708823648551</v>
       </c>
       <c r="E87">
-        <v>1203.139999999999</v>
+        <v>1278.944</v>
       </c>
       <c r="F87">
-        <v>6443.339999999999</v>
+        <v>6519.143999999999</v>
       </c>
       <c r="G87">
         <v>181.8</v>
@@ -8409,37 +8409,37 @@
         <v>74.5</v>
       </c>
       <c r="M87">
-        <v>1519.339572</v>
+        <v>1537.2141552</v>
       </c>
       <c r="N87">
-        <v>-1444.839572</v>
+        <v>-1462.7141552</v>
       </c>
       <c r="O87">
-        <v>-288.9679144</v>
+        <v>-292.54283104</v>
       </c>
       <c r="P87">
-        <v>-1155.8716576</v>
+        <v>-1170.17132416</v>
       </c>
       <c r="Q87">
-        <v>-1131.3716576</v>
+        <v>-1145.67132416</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2567198214008513</v>
+        <v>0.2717855229294835</v>
       </c>
       <c r="T87">
-        <v>3.262862556529711</v>
+        <v>3.495924167710406</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.00980689259635765</v>
+        <v>0.009692858961516284</v>
       </c>
       <c r="W87">
-        <v>0.2334875347257789</v>
+        <v>0.2335144238568745</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.04903446298178826</v>
+        <v>0.04846429480758141</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2388723777270397</v>
+        <v>0.2407723777270397</v>
       </c>
       <c r="C88">
-        <v>-4989.635176351449</v>
+        <v>-5078.572558601714</v>
       </c>
       <c r="D88">
-        <v>1347.708823648551</v>
+        <v>1334.575441398286</v>
       </c>
       <c r="E88">
-        <v>1278.944</v>
+        <v>1354.748</v>
       </c>
       <c r="F88">
-        <v>6519.143999999999</v>
+        <v>6594.947999999999</v>
       </c>
       <c r="G88">
         <v>181.8</v>
@@ -8491,37 +8491,37 @@
         <v>74.5</v>
       </c>
       <c r="M88">
-        <v>1537.2141552</v>
+        <v>1555.0887384</v>
       </c>
       <c r="N88">
-        <v>-1462.7141552</v>
+        <v>-1480.5887384</v>
       </c>
       <c r="O88">
-        <v>-292.54283104</v>
+        <v>-296.11774768</v>
       </c>
       <c r="P88">
-        <v>-1170.17132416</v>
+        <v>-1184.47099072</v>
       </c>
       <c r="Q88">
-        <v>-1145.67132416</v>
+        <v>-1159.97099072</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2717855229294835</v>
+        <v>0.2891690246932899</v>
       </c>
       <c r="T88">
-        <v>3.495924167710406</v>
+        <v>3.764841411380436</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.009692858961516284</v>
+        <v>0.009581446789544831</v>
       </c>
       <c r="W88">
-        <v>0.2335144238568745</v>
+        <v>0.2335406948470253</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.04846429480758141</v>
+        <v>0.04790723394772411</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2407723777270397</v>
+        <v>0.2426723777270397</v>
       </c>
       <c r="C89">
-        <v>-5078.572558601714</v>
+        <v>-5167.256442351441</v>
       </c>
       <c r="D89">
-        <v>1334.575441398286</v>
+        <v>1321.695557648558</v>
       </c>
       <c r="E89">
-        <v>1354.748</v>
+        <v>1430.552</v>
       </c>
       <c r="F89">
-        <v>6594.947999999999</v>
+        <v>6670.751999999999</v>
       </c>
       <c r="G89">
         <v>181.8</v>
@@ -8573,37 +8573,37 @@
         <v>74.5</v>
       </c>
       <c r="M89">
-        <v>1555.0887384</v>
+        <v>1572.9633216</v>
       </c>
       <c r="N89">
-        <v>-1480.5887384</v>
+        <v>-1498.4633216</v>
       </c>
       <c r="O89">
-        <v>-296.11774768</v>
+        <v>-299.69266432</v>
       </c>
       <c r="P89">
-        <v>-1184.47099072</v>
+        <v>-1198.77065728</v>
       </c>
       <c r="Q89">
-        <v>-1159.97099072</v>
+        <v>-1174.27065728</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2891690246932899</v>
+        <v>0.3094497767510641</v>
       </c>
       <c r="T89">
-        <v>3.764841411380436</v>
+        <v>4.07857819566214</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.009581446789544831</v>
+        <v>0.009472566712390912</v>
       </c>
       <c r="W89">
-        <v>0.2335406948470253</v>
+        <v>0.2335663687692182</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.04790723394772411</v>
+        <v>0.04736283356195459</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2426723777270397</v>
+        <v>0.2445723777270397</v>
       </c>
       <c r="C90">
-        <v>-5167.256442351441</v>
+        <v>-5255.694096927838</v>
       </c>
       <c r="D90">
-        <v>1321.695557648558</v>
+        <v>1309.061903072162</v>
       </c>
       <c r="E90">
-        <v>1430.552</v>
+        <v>1506.356</v>
       </c>
       <c r="F90">
-        <v>6670.751999999999</v>
+        <v>6746.556</v>
       </c>
       <c r="G90">
         <v>181.8</v>
@@ -8655,37 +8655,37 @@
         <v>74.5</v>
       </c>
       <c r="M90">
-        <v>1572.9633216</v>
+        <v>1590.8379048</v>
       </c>
       <c r="N90">
-        <v>-1498.4633216</v>
+        <v>-1516.3379048</v>
       </c>
       <c r="O90">
-        <v>-299.69266432</v>
+        <v>-303.26758096</v>
       </c>
       <c r="P90">
-        <v>-1198.77065728</v>
+        <v>-1213.07032384</v>
       </c>
       <c r="Q90">
-        <v>-1174.27065728</v>
+        <v>-1188.57032384</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3094497767510641</v>
+        <v>0.3334179382738882</v>
       </c>
       <c r="T90">
-        <v>4.07857819566214</v>
+        <v>4.449358031631426</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.009472566712390912</v>
+        <v>0.009366133378543823</v>
       </c>
       <c r="W90">
-        <v>0.2335663687692182</v>
+        <v>0.2335914657493394</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.04736283356195459</v>
+        <v>0.04683066689271909</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2445723777270397</v>
+        <v>0.2464723777270397</v>
       </c>
       <c r="C91">
-        <v>-5255.694096927838</v>
+        <v>-5343.89251634923</v>
       </c>
       <c r="D91">
-        <v>1309.061903072162</v>
+        <v>1296.667483650769</v>
       </c>
       <c r="E91">
-        <v>1506.356</v>
+        <v>1582.16</v>
       </c>
       <c r="F91">
-        <v>6746.556</v>
+        <v>6822.36</v>
       </c>
       <c r="G91">
         <v>181.8</v>
@@ -8737,37 +8737,37 @@
         <v>74.5</v>
       </c>
       <c r="M91">
-        <v>1590.8379048</v>
+        <v>1608.712488</v>
       </c>
       <c r="N91">
-        <v>-1516.3379048</v>
+        <v>-1534.212488</v>
       </c>
       <c r="O91">
-        <v>-303.26758096</v>
+        <v>-306.8424976</v>
       </c>
       <c r="P91">
-        <v>-1213.07032384</v>
+        <v>-1227.3699904</v>
       </c>
       <c r="Q91">
-        <v>-1188.57032384</v>
+        <v>-1202.8699904</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3334179382738882</v>
+        <v>0.362179732101277</v>
       </c>
       <c r="T91">
-        <v>4.449358031631426</v>
+        <v>4.894293834794569</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.009366133378543823</v>
+        <v>0.009262065229893337</v>
       </c>
       <c r="W91">
-        <v>0.2335914657493394</v>
+        <v>0.2336160050187912</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.04683066689271909</v>
+        <v>0.04631032614946673</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2464723777270397</v>
+        <v>0.2483723777270398</v>
       </c>
       <c r="C92">
-        <v>-5343.89251634923</v>
+        <v>-5431.858432236184</v>
       </c>
       <c r="D92">
-        <v>1296.667483650769</v>
+        <v>1284.505567763815</v>
       </c>
       <c r="E92">
-        <v>1582.16</v>
+        <v>1657.964</v>
       </c>
       <c r="F92">
-        <v>6822.36</v>
+        <v>6898.164</v>
       </c>
       <c r="G92">
         <v>181.8</v>
@@ -8819,37 +8819,37 @@
         <v>74.5</v>
       </c>
       <c r="M92">
-        <v>1608.712488</v>
+        <v>1626.5870712</v>
       </c>
       <c r="N92">
-        <v>-1534.212488</v>
+        <v>-1552.0870712</v>
       </c>
       <c r="O92">
-        <v>-306.8424976</v>
+        <v>-310.41741424</v>
       </c>
       <c r="P92">
-        <v>-1227.3699904</v>
+        <v>-1241.66965696</v>
       </c>
       <c r="Q92">
-        <v>-1202.8699904</v>
+        <v>-1217.16965696</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.362179732101277</v>
+        <v>0.3973330356680856</v>
       </c>
       <c r="T92">
-        <v>4.894293834794569</v>
+        <v>5.438104260882855</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.009262065229893337</v>
+        <v>0.009160284293301102</v>
       </c>
       <c r="W92">
-        <v>0.2336160050187912</v>
+        <v>0.2336400049636396</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.04631032614946673</v>
+        <v>0.04580142146650545</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2483723777270398</v>
+        <v>0.2502723777270398</v>
       </c>
       <c r="C93">
-        <v>-5431.858432236184</v>
+        <v>-5519.598326002771</v>
       </c>
       <c r="D93">
-        <v>1284.505567763815</v>
+        <v>1272.569673997229</v>
       </c>
       <c r="E93">
-        <v>1657.964</v>
+        <v>1733.768</v>
       </c>
       <c r="F93">
-        <v>6898.164</v>
+        <v>6973.968</v>
       </c>
       <c r="G93">
         <v>181.8</v>
@@ -8901,37 +8901,37 @@
         <v>74.5</v>
       </c>
       <c r="M93">
-        <v>1626.5870712</v>
+        <v>1644.4616544</v>
       </c>
       <c r="N93">
-        <v>-1552.0870712</v>
+        <v>-1569.9616544</v>
       </c>
       <c r="O93">
-        <v>-310.41741424</v>
+        <v>-313.9923308800001</v>
       </c>
       <c r="P93">
-        <v>-1241.66965696</v>
+        <v>-1255.96932352</v>
       </c>
       <c r="Q93">
-        <v>-1217.16965696</v>
+        <v>-1231.46932352</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3973330356680856</v>
+        <v>0.4412746651265965</v>
       </c>
       <c r="T93">
-        <v>5.438104260882855</v>
+        <v>6.117867293493214</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.009160284293301102</v>
+        <v>0.00906071598576522</v>
       </c>
       <c r="W93">
-        <v>0.2336400049636396</v>
+        <v>0.2336634831705566</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.04580142146650545</v>
+        <v>0.04530357992882605</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2502723777270398</v>
+        <v>0.2521723777270398</v>
       </c>
       <c r="C94">
-        <v>-5519.598326002771</v>
+        <v>-5607.118440374398</v>
       </c>
       <c r="D94">
-        <v>1272.569673997229</v>
+        <v>1260.853559625602</v>
       </c>
       <c r="E94">
-        <v>1733.768</v>
+        <v>1809.572</v>
       </c>
       <c r="F94">
-        <v>6973.968</v>
+        <v>7049.772</v>
       </c>
       <c r="G94">
         <v>181.8</v>
@@ -8983,37 +8983,37 @@
         <v>74.5</v>
       </c>
       <c r="M94">
-        <v>1644.4616544</v>
+        <v>1662.3362376</v>
       </c>
       <c r="N94">
-        <v>-1569.9616544</v>
+        <v>-1587.8362376</v>
       </c>
       <c r="O94">
-        <v>-313.9923308800001</v>
+        <v>-317.56724752</v>
       </c>
       <c r="P94">
-        <v>-1255.96932352</v>
+        <v>-1270.26899008</v>
       </c>
       <c r="Q94">
-        <v>-1231.46932352</v>
+        <v>-1245.76899008</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4412746651265965</v>
+        <v>0.4977710458589674</v>
       </c>
       <c r="T94">
-        <v>6.117867293493214</v>
+        <v>6.991848335420817</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.00906071598576522</v>
+        <v>0.008963288932154841</v>
       </c>
       <c r="W94">
-        <v>0.2336634831705566</v>
+        <v>0.2336864564697979</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.04530357992882605</v>
+        <v>0.04481644466077417</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2521723777270398</v>
+        <v>0.2540723777270398</v>
       </c>
       <c r="C95">
-        <v>-5607.118440374398</v>
+        <v>-5694.424790275202</v>
       </c>
       <c r="D95">
-        <v>1260.853559625602</v>
+        <v>1249.351209724798</v>
       </c>
       <c r="E95">
-        <v>1809.572</v>
+        <v>1885.376</v>
       </c>
       <c r="F95">
-        <v>7049.772</v>
+        <v>7125.576</v>
       </c>
       <c r="G95">
         <v>181.8</v>
@@ -9065,37 +9065,37 @@
         <v>74.5</v>
       </c>
       <c r="M95">
-        <v>1662.3362376</v>
+        <v>1680.2108208</v>
       </c>
       <c r="N95">
-        <v>-1587.8362376</v>
+        <v>-1605.7108208</v>
       </c>
       <c r="O95">
-        <v>-317.56724752</v>
+        <v>-321.14216416</v>
       </c>
       <c r="P95">
-        <v>-1270.26899008</v>
+        <v>-1284.56865664</v>
       </c>
       <c r="Q95">
-        <v>-1245.76899008</v>
+        <v>-1260.06865664</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4977710458589674</v>
+        <v>0.5730995535021286</v>
       </c>
       <c r="T95">
-        <v>6.991848335420817</v>
+        <v>8.157156391324287</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.008963288932154841</v>
+        <v>0.008867934794578727</v>
       </c>
       <c r="W95">
-        <v>0.2336864564697979</v>
+        <v>0.2337089409754383</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.04481644466077417</v>
+        <v>0.04433967397289362</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2540723777270398</v>
+        <v>0.2559723777270398</v>
       </c>
       <c r="C96">
-        <v>-5694.424790275202</v>
+        <v>-5781.523173124883</v>
       </c>
       <c r="D96">
-        <v>1249.351209724798</v>
+        <v>1238.056826875117</v>
       </c>
       <c r="E96">
-        <v>1885.376</v>
+        <v>1961.18</v>
       </c>
       <c r="F96">
-        <v>7125.576</v>
+        <v>7201.38</v>
       </c>
       <c r="G96">
         <v>181.8</v>
@@ -9147,37 +9147,37 @@
         <v>74.5</v>
       </c>
       <c r="M96">
-        <v>1680.2108208</v>
+        <v>1698.085404</v>
       </c>
       <c r="N96">
-        <v>-1605.7108208</v>
+        <v>-1623.585404</v>
       </c>
       <c r="O96">
-        <v>-321.14216416</v>
+        <v>-324.7170808000001</v>
       </c>
       <c r="P96">
-        <v>-1284.56865664</v>
+        <v>-1298.8683232</v>
       </c>
       <c r="Q96">
-        <v>-1260.06865664</v>
+        <v>-1274.3683232</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5730995535021286</v>
+        <v>0.6785594642025549</v>
       </c>
       <c r="T96">
-        <v>8.157156391324287</v>
+        <v>9.788587669589152</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.008867934794578727</v>
+        <v>0.008774588112530528</v>
       </c>
       <c r="W96">
-        <v>0.2337089409754383</v>
+        <v>0.2337309521230653</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.04433967397289362</v>
+        <v>0.04387294056265267</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2559723777270398</v>
+        <v>0.2578723777270397</v>
       </c>
       <c r="C97">
-        <v>-5781.523173124883</v>
+        <v>-5868.41917858205</v>
       </c>
       <c r="D97">
-        <v>1238.056826875117</v>
+        <v>1226.96482141795</v>
       </c>
       <c r="E97">
-        <v>1961.18</v>
+        <v>2036.984</v>
       </c>
       <c r="F97">
-        <v>7201.38</v>
+        <v>7277.184</v>
       </c>
       <c r="G97">
         <v>181.8</v>
@@ -9229,37 +9229,37 @@
         <v>74.5</v>
       </c>
       <c r="M97">
-        <v>1698.085404</v>
+        <v>1715.9599872</v>
       </c>
       <c r="N97">
-        <v>-1623.585404</v>
+        <v>-1641.4599872</v>
       </c>
       <c r="O97">
-        <v>-324.7170808000001</v>
+        <v>-328.29199744</v>
       </c>
       <c r="P97">
-        <v>-1298.8683232</v>
+        <v>-1313.16798976</v>
       </c>
       <c r="Q97">
-        <v>-1274.3683232</v>
+        <v>-1288.66798976</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6785594642025549</v>
+        <v>0.8367493302531939</v>
       </c>
       <c r="T97">
-        <v>9.788587669589152</v>
+        <v>12.23573458698644</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.008774588112530528</v>
+        <v>0.008683186153025003</v>
       </c>
       <c r="W97">
-        <v>0.2337309521230653</v>
+        <v>0.2337525047051167</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.04387294056265267</v>
+        <v>0.04341593076512495</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2578723777270397</v>
+        <v>0.2597723777270398</v>
       </c>
       <c r="C98">
-        <v>-5868.419178582049</v>
+        <v>-5955.118197768442</v>
       </c>
       <c r="D98">
-        <v>1226.96482141795</v>
+        <v>1216.069802231558</v>
       </c>
       <c r="E98">
-        <v>2036.983999999999</v>
+        <v>2112.788</v>
       </c>
       <c r="F98">
-        <v>7277.183999999999</v>
+        <v>7352.987999999999</v>
       </c>
       <c r="G98">
         <v>181.8</v>
@@ -9311,37 +9311,37 @@
         <v>74.5</v>
       </c>
       <c r="M98">
-        <v>1715.9599872</v>
+        <v>1733.8345704</v>
       </c>
       <c r="N98">
-        <v>-1641.4599872</v>
+        <v>-1659.3345704</v>
       </c>
       <c r="O98">
-        <v>-328.29199744</v>
+        <v>-331.86691408</v>
       </c>
       <c r="P98">
-        <v>-1313.16798976</v>
+        <v>-1327.46765632</v>
       </c>
       <c r="Q98">
-        <v>-1288.66798976</v>
+        <v>-1302.96765632</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8367493302531916</v>
+        <v>1.100399107004256</v>
       </c>
       <c r="T98">
-        <v>12.23573458698641</v>
+        <v>16.31431278264855</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.008683186153025003</v>
+        <v>0.008593668770004127</v>
       </c>
       <c r="W98">
-        <v>0.2337525047051167</v>
+        <v>0.233773612904033</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.04341593076512507</v>
+        <v>0.04296834385002068</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2597723777270398</v>
+        <v>0.2616723777270397</v>
       </c>
       <c r="C99">
-        <v>-5955.118197768442</v>
+        <v>-6041.625432006042</v>
       </c>
       <c r="D99">
-        <v>1216.069802231558</v>
+        <v>1205.366567993958</v>
       </c>
       <c r="E99">
-        <v>2112.788</v>
+        <v>2188.592</v>
       </c>
       <c r="F99">
-        <v>7352.987999999999</v>
+        <v>7428.791999999999</v>
       </c>
       <c r="G99">
         <v>181.8</v>
@@ -9393,37 +9393,37 @@
         <v>74.5</v>
       </c>
       <c r="M99">
-        <v>1733.8345704</v>
+        <v>1751.7091536</v>
       </c>
       <c r="N99">
-        <v>-1659.3345704</v>
+        <v>-1677.2091536</v>
       </c>
       <c r="O99">
-        <v>-331.86691408</v>
+        <v>-335.44183072</v>
       </c>
       <c r="P99">
-        <v>-1327.46765632</v>
+        <v>-1341.76732288</v>
       </c>
       <c r="Q99">
-        <v>-1302.96765632</v>
+        <v>-1317.26732288</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.100399107004256</v>
+        <v>1.627698660506383</v>
       </c>
       <c r="T99">
-        <v>16.31431278264855</v>
+        <v>24.47146917397282</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.008593668770004127</v>
+        <v>0.008505978272351023</v>
       </c>
       <c r="W99">
-        <v>0.233773612904033</v>
+        <v>0.2337942903233796</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.04296834385002068</v>
+        <v>0.04252989136175511</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2616723777270397</v>
+        <v>0.2635723777270397</v>
       </c>
       <c r="C100">
-        <v>-6041.625432006042</v>
+        <v>-6127.945901096805</v>
       </c>
       <c r="D100">
-        <v>1205.366567993958</v>
+        <v>1194.850098903195</v>
       </c>
       <c r="E100">
-        <v>2188.592</v>
+        <v>2264.396</v>
       </c>
       <c r="F100">
-        <v>7428.791999999999</v>
+        <v>7504.596</v>
       </c>
       <c r="G100">
         <v>181.8</v>
@@ -9475,37 +9475,37 @@
         <v>74.5</v>
       </c>
       <c r="M100">
-        <v>1751.7091536</v>
+        <v>1769.5837368</v>
       </c>
       <c r="N100">
-        <v>-1677.2091536</v>
+        <v>-1695.0837368</v>
       </c>
       <c r="O100">
-        <v>-335.44183072</v>
+        <v>-339.01674736</v>
       </c>
       <c r="P100">
-        <v>-1341.76732288</v>
+        <v>-1356.06698944</v>
       </c>
       <c r="Q100">
-        <v>-1317.26732288</v>
+        <v>-1331.56698944</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.627698660506383</v>
+        <v>3.209597321012767</v>
       </c>
       <c r="T100">
-        <v>24.47146917397282</v>
+        <v>48.94293834794564</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.008505978272351023</v>
+        <v>0.008420059299903032</v>
       </c>
       <c r="W100">
-        <v>0.2337942903233796</v>
+        <v>0.2338145500170829</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.04252989136175511</v>
+        <v>0.04210029649951519</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2635723777270397</v>
-      </c>
-      <c r="C101">
-        <v>-6127.945901096805</v>
-      </c>
-      <c r="D101">
-        <v>1194.850098903195</v>
-      </c>
-      <c r="E101">
-        <v>2264.396</v>
-      </c>
-      <c r="F101">
-        <v>7504.596</v>
-      </c>
-      <c r="G101">
-        <v>181.8</v>
-      </c>
-      <c r="H101">
-        <v>2340.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>99</v>
-      </c>
-      <c r="K101">
-        <v>24.5</v>
-      </c>
-      <c r="L101">
-        <v>74.5</v>
-      </c>
-      <c r="M101">
-        <v>1769.5837368</v>
-      </c>
-      <c r="N101">
-        <v>-1695.0837368</v>
-      </c>
-      <c r="O101">
-        <v>-339.01674736</v>
-      </c>
-      <c r="P101">
-        <v>-1356.06698944</v>
-      </c>
-      <c r="Q101">
-        <v>-1331.56698944</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.209597321012767</v>
-      </c>
-      <c r="T101">
-        <v>48.94293834794564</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.008420059299903032</v>
-      </c>
-      <c r="W101">
-        <v>0.2338145500170829</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.04210029649951519</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
